--- a/research/traditional_assets/database/data/jamaica/jamaica_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/jamaica/jamaica_r_e_i_t.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09767793992561302</v>
+        <v>0.09746749507579898</v>
       </c>
       <c r="C2">
-        <v>89.43919896641907</v>
+        <v>88.97519381994545</v>
       </c>
       <c r="D2">
-        <v>85.92919896641907</v>
+        <v>86.27919381994545</v>
       </c>
       <c r="E2">
-        <v>-27</v>
+        <v>-26.186</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="G2">
         <v>3.51</v>
@@ -1451,28 +1451,28 @@
         <v>3.1375</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0409442</v>
       </c>
       <c r="N2">
-        <v>3.1375</v>
+        <v>3.0965558</v>
       </c>
       <c r="O2">
-        <v>0.7843749999999999</v>
+        <v>0.7741389499999999</v>
       </c>
       <c r="P2">
-        <v>2.353125</v>
+        <v>2.32241685</v>
       </c>
       <c r="Q2">
-        <v>2.378125</v>
+        <v>2.34741685</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09767793992561302</v>
+        <v>0.09807095462201917</v>
       </c>
       <c r="T2">
-        <v>0.5016993284768603</v>
+        <v>0.5055000809653213</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>76.62868000840167</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09746749507579898</v>
+        <v>0.09725705022598496</v>
       </c>
       <c r="C3">
-        <v>88.97519381994545</v>
+        <v>88.51405143432041</v>
       </c>
       <c r="D3">
-        <v>86.27919381994545</v>
+        <v>86.6320514343204</v>
       </c>
       <c r="E3">
-        <v>-26.186</v>
+        <v>-25.372</v>
       </c>
       <c r="F3">
-        <v>0.8140000000000001</v>
+        <v>1.628</v>
       </c>
       <c r="G3">
         <v>3.51</v>
@@ -1533,28 +1533,28 @@
         <v>3.1375</v>
       </c>
       <c r="M3">
-        <v>0.0409442</v>
+        <v>0.0818884</v>
       </c>
       <c r="N3">
-        <v>3.0965558</v>
+        <v>3.0556116</v>
       </c>
       <c r="O3">
-        <v>0.7741389499999999</v>
+        <v>0.7639028999999999</v>
       </c>
       <c r="P3">
-        <v>2.32241685</v>
+        <v>2.2917087</v>
       </c>
       <c r="Q3">
-        <v>2.34741685</v>
+        <v>2.3167087</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09807095462201917</v>
+        <v>0.09847199002651527</v>
       </c>
       <c r="T3">
-        <v>0.5055000809653213</v>
+        <v>0.509378399831098</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>76.62868000840167</v>
+        <v>38.31434000420084</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09725705022598496</v>
+        <v>0.09704660537617092</v>
       </c>
       <c r="C4">
-        <v>88.51405143432041</v>
+        <v>88.05580707743769</v>
       </c>
       <c r="D4">
-        <v>86.6320514343204</v>
+        <v>86.98780707743769</v>
       </c>
       <c r="E4">
-        <v>-25.372</v>
+        <v>-24.558</v>
       </c>
       <c r="F4">
-        <v>1.628</v>
+        <v>2.442</v>
       </c>
       <c r="G4">
         <v>3.51</v>
@@ -1615,28 +1615,28 @@
         <v>3.1375</v>
       </c>
       <c r="M4">
-        <v>0.0818884</v>
+        <v>0.1228326</v>
       </c>
       <c r="N4">
-        <v>3.0556116</v>
+        <v>3.0146674</v>
       </c>
       <c r="O4">
-        <v>0.7639028999999999</v>
+        <v>0.7536668499999999</v>
       </c>
       <c r="P4">
-        <v>2.2917087</v>
+        <v>2.261000549999999</v>
       </c>
       <c r="Q4">
-        <v>2.3167087</v>
+        <v>2.286000549999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09847199002651527</v>
+        <v>0.09888129420223807</v>
       </c>
       <c r="T4">
-        <v>0.509378399831098</v>
+        <v>0.5133366840343132</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.31434000420084</v>
+        <v>25.54289333613389</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09704660537617092</v>
+        <v>0.09683616052635689</v>
       </c>
       <c r="C5">
-        <v>88.05580707743769</v>
+        <v>87.60049659889198</v>
       </c>
       <c r="D5">
-        <v>86.98780707743769</v>
+        <v>87.34649659889197</v>
       </c>
       <c r="E5">
-        <v>-24.558</v>
+        <v>-23.744</v>
       </c>
       <c r="F5">
-        <v>2.442</v>
+        <v>3.256</v>
       </c>
       <c r="G5">
         <v>3.51</v>
@@ -1697,28 +1697,28 @@
         <v>3.1375</v>
       </c>
       <c r="M5">
-        <v>0.1228326</v>
+        <v>0.1637768</v>
       </c>
       <c r="N5">
-        <v>3.0146674</v>
+        <v>2.9737232</v>
       </c>
       <c r="O5">
-        <v>0.7536668499999999</v>
+        <v>0.7434307999999999</v>
       </c>
       <c r="P5">
-        <v>2.261000549999999</v>
+        <v>2.2302924</v>
       </c>
       <c r="Q5">
-        <v>2.286000549999999</v>
+        <v>2.2552924</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09888129420223807</v>
+        <v>0.09929912554828843</v>
       </c>
       <c r="T5">
-        <v>0.5133366840343132</v>
+        <v>0.5173774324917622</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.54289333613389</v>
+        <v>19.15717000210042</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09683616052635689</v>
+        <v>0.09662571567654286</v>
       </c>
       <c r="C6">
-        <v>87.60049659889198</v>
+        <v>87.14815644202173</v>
       </c>
       <c r="D6">
-        <v>87.34649659889197</v>
+        <v>87.70815644202173</v>
       </c>
       <c r="E6">
-        <v>-23.744</v>
+        <v>-22.93</v>
       </c>
       <c r="F6">
-        <v>3.256</v>
+        <v>4.07</v>
       </c>
       <c r="G6">
         <v>3.51</v>
@@ -1779,28 +1779,28 @@
         <v>3.1375</v>
       </c>
       <c r="M6">
-        <v>0.1637768</v>
+        <v>0.204721</v>
       </c>
       <c r="N6">
-        <v>2.9737232</v>
+        <v>2.932779</v>
       </c>
       <c r="O6">
-        <v>0.7434307999999999</v>
+        <v>0.7331947499999999</v>
       </c>
       <c r="P6">
-        <v>2.2302924</v>
+        <v>2.19958425</v>
       </c>
       <c r="Q6">
-        <v>2.2552924</v>
+        <v>2.224584249999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09929912554828843</v>
+        <v>0.09972575334372932</v>
       </c>
       <c r="T6">
-        <v>0.5173774324917622</v>
+        <v>0.521503249337789</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.15717000210042</v>
+        <v>15.32573600168033</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09662571567654286</v>
+        <v>0.09648277082672882</v>
       </c>
       <c r="C7">
-        <v>87.14815644202173</v>
+        <v>86.58152707795111</v>
       </c>
       <c r="D7">
-        <v>87.70815644202173</v>
+        <v>87.9555270779511</v>
       </c>
       <c r="E7">
-        <v>-22.93</v>
+        <v>-22.116</v>
       </c>
       <c r="F7">
-        <v>4.07</v>
+        <v>4.884</v>
       </c>
       <c r="G7">
         <v>3.51</v>
@@ -1861,45 +1861,45 @@
         <v>3.1375</v>
       </c>
       <c r="M7">
-        <v>0.204721</v>
+        <v>0.2529912</v>
       </c>
       <c r="N7">
-        <v>2.932779</v>
+        <v>2.8845088</v>
       </c>
       <c r="O7">
-        <v>0.7331947499999999</v>
+        <v>0.7211272</v>
       </c>
       <c r="P7">
-        <v>2.19958425</v>
+        <v>2.1633816</v>
       </c>
       <c r="Q7">
-        <v>2.224584249999999</v>
+        <v>2.1883816</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09972575334372932</v>
+        <v>0.1001614583263073</v>
       </c>
       <c r="T7">
-        <v>0.521503249337789</v>
+        <v>0.5257168495209653</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>15.32573600168033</v>
+        <v>12.40161713134686</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09648277082672882</v>
+        <v>0.0962835759769148</v>
       </c>
       <c r="C8">
-        <v>86.58152707795111</v>
+        <v>86.11457634432278</v>
       </c>
       <c r="D8">
-        <v>87.9555270779511</v>
+        <v>88.30257634432277</v>
       </c>
       <c r="E8">
-        <v>-22.116</v>
+        <v>-21.302</v>
       </c>
       <c r="F8">
-        <v>4.884</v>
+        <v>5.698</v>
       </c>
       <c r="G8">
         <v>3.51</v>
@@ -1943,28 +1943,28 @@
         <v>3.1375</v>
       </c>
       <c r="M8">
-        <v>0.2529912</v>
+        <v>0.2951564</v>
       </c>
       <c r="N8">
-        <v>2.8845088</v>
+        <v>2.8423436</v>
       </c>
       <c r="O8">
-        <v>0.7211272</v>
+        <v>0.7105858999999999</v>
       </c>
       <c r="P8">
-        <v>2.1633816</v>
+        <v>2.1317577</v>
       </c>
       <c r="Q8">
-        <v>2.1883816</v>
+        <v>2.1567577</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1001614583263073</v>
+        <v>0.1006065333085105</v>
       </c>
       <c r="T8">
-        <v>0.5257168495209653</v>
+        <v>0.5300210647618443</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.40161713134686</v>
+        <v>10.62995754115445</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09628357597691478</v>
+        <v>0.09618638112710078</v>
       </c>
       <c r="C9">
-        <v>86.11457634432278</v>
+        <v>85.47091117397302</v>
       </c>
       <c r="D9">
-        <v>88.30257634432279</v>
+        <v>88.47291117397302</v>
       </c>
       <c r="E9">
-        <v>-21.302</v>
+        <v>-20.488</v>
       </c>
       <c r="F9">
-        <v>5.698000000000001</v>
+        <v>6.512</v>
       </c>
       <c r="G9">
         <v>3.51</v>
@@ -2025,45 +2025,45 @@
         <v>3.1375</v>
       </c>
       <c r="M9">
-        <v>0.2951564</v>
+        <v>0.348392</v>
       </c>
       <c r="N9">
-        <v>2.8423436</v>
+        <v>2.789108</v>
       </c>
       <c r="O9">
-        <v>0.7105858999999999</v>
+        <v>0.6972769999999999</v>
       </c>
       <c r="P9">
-        <v>2.1317577</v>
+        <v>2.091831</v>
       </c>
       <c r="Q9">
-        <v>2.1567577</v>
+        <v>2.116831</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1006065333085105</v>
+        <v>0.1010612838338052</v>
       </c>
       <c r="T9">
-        <v>0.5300210647618443</v>
+        <v>0.5344188498992642</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>10.62995754115445</v>
+        <v>9.005660290707018</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09618638112710078</v>
+        <v>0.09599993627728673</v>
       </c>
       <c r="C10">
-        <v>85.47091117397302</v>
+        <v>84.98550359579062</v>
       </c>
       <c r="D10">
-        <v>88.47291117397302</v>
+        <v>88.80150359579061</v>
       </c>
       <c r="E10">
-        <v>-20.488</v>
+        <v>-19.674</v>
       </c>
       <c r="F10">
-        <v>6.512</v>
+        <v>7.326000000000001</v>
       </c>
       <c r="G10">
         <v>3.51</v>
@@ -2107,28 +2107,28 @@
         <v>3.1375</v>
       </c>
       <c r="M10">
-        <v>0.348392</v>
+        <v>0.391941</v>
       </c>
       <c r="N10">
-        <v>2.789108</v>
+        <v>2.745559</v>
       </c>
       <c r="O10">
-        <v>0.6972769999999999</v>
+        <v>0.6863897499999999</v>
       </c>
       <c r="P10">
-        <v>2.091831</v>
+        <v>2.05916925</v>
       </c>
       <c r="Q10">
-        <v>2.116831</v>
+        <v>2.08416925</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1010612838338052</v>
+        <v>0.1015260288761393</v>
       </c>
       <c r="T10">
-        <v>0.5344188498992642</v>
+        <v>0.5389132896550889</v>
       </c>
       <c r="U10">
         <v>0.0535</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>9.005660290707018</v>
+        <v>8.005031369517349</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09599993627728673</v>
+        <v>0.0958734914274727</v>
       </c>
       <c r="C11">
-        <v>84.98550359579062</v>
+        <v>84.3957438567617</v>
       </c>
       <c r="D11">
-        <v>88.80150359579061</v>
+        <v>89.02574385676169</v>
       </c>
       <c r="E11">
-        <v>-19.674</v>
+        <v>-18.86</v>
       </c>
       <c r="F11">
-        <v>7.326000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G11">
         <v>3.51</v>
@@ -2189,45 +2189,45 @@
         <v>3.1375</v>
       </c>
       <c r="M11">
-        <v>0.391941</v>
+        <v>0.4420020000000001</v>
       </c>
       <c r="N11">
-        <v>2.745559</v>
+        <v>2.695498</v>
       </c>
       <c r="O11">
-        <v>0.6863897499999999</v>
+        <v>0.6738744999999999</v>
       </c>
       <c r="P11">
-        <v>2.05916925</v>
+        <v>2.0216235</v>
       </c>
       <c r="Q11">
-        <v>2.08416925</v>
+        <v>2.046623499999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1015260288761393</v>
+        <v>0.1020011015860808</v>
       </c>
       <c r="T11">
-        <v>0.5389132896550889</v>
+        <v>0.543507605849932</v>
       </c>
       <c r="U11">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y11">
-        <v>8.005031369517349</v>
+        <v>7.098384170207373</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0958734914274727</v>
+        <v>0.09569304657765869</v>
       </c>
       <c r="C12">
-        <v>84.3957438567617</v>
+        <v>83.90371731963313</v>
       </c>
       <c r="D12">
-        <v>89.02574385676169</v>
+        <v>89.34771731963312</v>
       </c>
       <c r="E12">
-        <v>-18.86</v>
+        <v>-18.046</v>
       </c>
       <c r="F12">
-        <v>8.140000000000001</v>
+        <v>8.954000000000001</v>
       </c>
       <c r="G12">
         <v>3.51</v>
@@ -2271,28 +2271,28 @@
         <v>3.1375</v>
       </c>
       <c r="M12">
-        <v>0.4420020000000001</v>
+        <v>0.4862022</v>
       </c>
       <c r="N12">
-        <v>2.695498</v>
+        <v>2.6512978</v>
       </c>
       <c r="O12">
-        <v>0.6738744999999999</v>
+        <v>0.6628244499999999</v>
       </c>
       <c r="P12">
-        <v>2.0216235</v>
+        <v>1.98847335</v>
       </c>
       <c r="Q12">
-        <v>2.046623499999999</v>
+        <v>2.013473349999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1020011015860808</v>
+        <v>0.1024868500872569</v>
       </c>
       <c r="T12">
-        <v>0.543507605849932</v>
+        <v>0.5482051651053333</v>
       </c>
       <c r="U12">
         <v>0.0543</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.098384170207373</v>
+        <v>6.45307651837034</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09569304657765869</v>
+        <v>0.09560260172784463</v>
       </c>
       <c r="C13">
-        <v>83.90371731963313</v>
+        <v>83.25197873959596</v>
       </c>
       <c r="D13">
-        <v>89.34771731963312</v>
+        <v>89.50997873959595</v>
       </c>
       <c r="E13">
-        <v>-18.046</v>
+        <v>-17.232</v>
       </c>
       <c r="F13">
-        <v>8.954000000000001</v>
+        <v>9.768000000000001</v>
       </c>
       <c r="G13">
         <v>3.51</v>
@@ -2353,45 +2353,45 @@
         <v>3.1375</v>
       </c>
       <c r="M13">
-        <v>0.4862022</v>
+        <v>0.5401704000000001</v>
       </c>
       <c r="N13">
-        <v>2.6512978</v>
+        <v>2.5973296</v>
       </c>
       <c r="O13">
-        <v>0.6628244499999999</v>
+        <v>0.6493323999999999</v>
       </c>
       <c r="P13">
-        <v>1.98847335</v>
+        <v>1.9479972</v>
       </c>
       <c r="Q13">
-        <v>2.013473349999999</v>
+        <v>1.9729972</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1024868500872569</v>
+        <v>0.1029836383270962</v>
       </c>
       <c r="T13">
-        <v>0.5482051651053333</v>
+        <v>0.5530094870710847</v>
       </c>
       <c r="U13">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.45307651837034</v>
+        <v>5.808352327339668</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09560260172784463</v>
+        <v>0.09542965687803059</v>
       </c>
       <c r="C14">
-        <v>83.25197873959596</v>
+        <v>82.74989485596205</v>
       </c>
       <c r="D14">
-        <v>89.50997873959595</v>
+        <v>89.82189485596204</v>
       </c>
       <c r="E14">
-        <v>-17.232</v>
+        <v>-16.418</v>
       </c>
       <c r="F14">
-        <v>9.768000000000001</v>
+        <v>10.582</v>
       </c>
       <c r="G14">
         <v>3.51</v>
@@ -2435,28 +2435,28 @@
         <v>3.1375</v>
       </c>
       <c r="M14">
-        <v>0.5401704000000001</v>
+        <v>0.5851846000000001</v>
       </c>
       <c r="N14">
-        <v>2.5973296</v>
+        <v>2.552315399999999</v>
       </c>
       <c r="O14">
-        <v>0.6493323999999999</v>
+        <v>0.6380788499999999</v>
       </c>
       <c r="P14">
-        <v>1.9479972</v>
+        <v>1.91423655</v>
       </c>
       <c r="Q14">
-        <v>1.9729972</v>
+        <v>1.93923655</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1029836383270962</v>
+        <v>0.1034918469862421</v>
       </c>
       <c r="T14">
-        <v>0.5530094870710847</v>
+        <v>0.5579242532199566</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.808352327339668</v>
+        <v>5.361555994467386</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09542965687803059</v>
+        <v>0.09525671202821658</v>
       </c>
       <c r="C15">
-        <v>82.74989485596205</v>
+        <v>82.24999244714466</v>
       </c>
       <c r="D15">
-        <v>89.82189485596204</v>
+        <v>90.13599244714466</v>
       </c>
       <c r="E15">
-        <v>-16.418</v>
+        <v>-15.604</v>
       </c>
       <c r="F15">
-        <v>10.582</v>
+        <v>11.396</v>
       </c>
       <c r="G15">
         <v>3.51</v>
@@ -2517,28 +2517,28 @@
         <v>3.1375</v>
       </c>
       <c r="M15">
-        <v>0.5851846000000001</v>
+        <v>0.6301988000000002</v>
       </c>
       <c r="N15">
-        <v>2.552315399999999</v>
+        <v>2.5073012</v>
       </c>
       <c r="O15">
-        <v>0.6380788499999999</v>
+        <v>0.6268252999999999</v>
       </c>
       <c r="P15">
-        <v>1.91423655</v>
+        <v>1.8804759</v>
       </c>
       <c r="Q15">
-        <v>1.93923655</v>
+        <v>1.9054759</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1034918469862421</v>
+        <v>0.1040118744514146</v>
       </c>
       <c r="T15">
-        <v>0.5579242532199566</v>
+        <v>0.5629533162560119</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.361555994467386</v>
+        <v>4.978587709148286</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09525671202821658</v>
+        <v>0.09508376717840253</v>
       </c>
       <c r="C16">
-        <v>82.24999244714466</v>
+        <v>81.7522944786063</v>
       </c>
       <c r="D16">
-        <v>90.13599244714466</v>
+        <v>90.45229447860631</v>
       </c>
       <c r="E16">
-        <v>-15.604</v>
+        <v>-14.79</v>
       </c>
       <c r="F16">
-        <v>11.396</v>
+        <v>12.21</v>
       </c>
       <c r="G16">
         <v>3.51</v>
@@ -2599,28 +2599,28 @@
         <v>3.1375</v>
       </c>
       <c r="M16">
-        <v>0.6301988000000002</v>
+        <v>0.6752130000000002</v>
       </c>
       <c r="N16">
-        <v>2.5073012</v>
+        <v>2.462286999999999</v>
       </c>
       <c r="O16">
-        <v>0.6268252999999999</v>
+        <v>0.6155717499999999</v>
       </c>
       <c r="P16">
-        <v>1.8804759</v>
+        <v>1.846715249999999</v>
       </c>
       <c r="Q16">
-        <v>1.9054759</v>
+        <v>1.871715249999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1040118744514146</v>
+        <v>0.1045441378569441</v>
       </c>
       <c r="T16">
-        <v>0.5629533162560119</v>
+        <v>0.5681007101870329</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>4.978587709148286</v>
+        <v>4.646681861871734</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09508376717840253</v>
+        <v>0.0952108223285885</v>
       </c>
       <c r="C17">
-        <v>81.7522944786063</v>
+        <v>80.70570515266432</v>
       </c>
       <c r="D17">
-        <v>90.45229447860631</v>
+        <v>90.21970515266432</v>
       </c>
       <c r="E17">
-        <v>-14.79</v>
+        <v>-13.976</v>
       </c>
       <c r="F17">
-        <v>12.21</v>
+        <v>13.024</v>
       </c>
       <c r="G17">
         <v>3.51</v>
@@ -2681,45 +2681,45 @@
         <v>3.1375</v>
       </c>
       <c r="M17">
-        <v>0.6752130000000001</v>
+        <v>0.7527872000000001</v>
       </c>
       <c r="N17">
-        <v>2.462287</v>
+        <v>2.3847128</v>
       </c>
       <c r="O17">
-        <v>0.61557175</v>
+        <v>0.5961781999999999</v>
       </c>
       <c r="P17">
-        <v>1.84671525</v>
+        <v>1.7885346</v>
       </c>
       <c r="Q17">
-        <v>1.87171525</v>
+        <v>1.8135346</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1045441378569441</v>
+        <v>0.1050890742007006</v>
       </c>
       <c r="T17">
-        <v>0.5681007101870329</v>
+        <v>0.5733706611164117</v>
       </c>
       <c r="U17">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.646681861871735</v>
+        <v>4.167844511702642</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0952108223285885</v>
+        <v>0.09550287747877448</v>
       </c>
       <c r="C18">
-        <v>80.70570515266432</v>
+        <v>79.36157227354987</v>
       </c>
       <c r="D18">
-        <v>90.21970515266432</v>
+        <v>89.68957227354987</v>
       </c>
       <c r="E18">
-        <v>-13.976</v>
+        <v>-13.162</v>
       </c>
       <c r="F18">
-        <v>13.024</v>
+        <v>13.838</v>
       </c>
       <c r="G18">
         <v>3.51</v>
@@ -2763,45 +2763,45 @@
         <v>3.1375</v>
       </c>
       <c r="M18">
-        <v>0.7527872000000001</v>
+        <v>0.8482694000000002</v>
       </c>
       <c r="N18">
-        <v>2.3847128</v>
+        <v>2.2892306</v>
       </c>
       <c r="O18">
-        <v>0.5961781999999999</v>
+        <v>0.5723076499999999</v>
       </c>
       <c r="P18">
-        <v>1.7885346</v>
+        <v>1.71692295</v>
       </c>
       <c r="Q18">
-        <v>1.8135346</v>
+        <v>1.74192295</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1050890742007006</v>
+        <v>0.1056471415406921</v>
       </c>
       <c r="T18">
-        <v>0.5733706611164117</v>
+        <v>0.5787675988151733</v>
       </c>
       <c r="U18">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.167844511702642</v>
+        <v>3.698707038117842</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09550287747877448</v>
+        <v>0.09575293262896042</v>
       </c>
       <c r="C19">
-        <v>79.36157227354987</v>
+        <v>78.09860284803963</v>
       </c>
       <c r="D19">
-        <v>89.68957227354987</v>
+        <v>89.24060284803963</v>
       </c>
       <c r="E19">
-        <v>-13.162</v>
+        <v>-12.348</v>
       </c>
       <c r="F19">
-        <v>13.838</v>
+        <v>14.652</v>
       </c>
       <c r="G19">
         <v>3.51</v>
@@ -2845,45 +2845,45 @@
         <v>3.1375</v>
       </c>
       <c r="M19">
-        <v>0.8482694000000002</v>
+        <v>0.9391932000000003</v>
       </c>
       <c r="N19">
-        <v>2.2892306</v>
+        <v>2.198306799999999</v>
       </c>
       <c r="O19">
-        <v>0.5723076499999999</v>
+        <v>0.5495766999999998</v>
       </c>
       <c r="P19">
-        <v>1.71692295</v>
+        <v>1.648730099999999</v>
       </c>
       <c r="Q19">
-        <v>1.74192295</v>
+        <v>1.673730099999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1056471415406921</v>
+        <v>0.10621882027922</v>
       </c>
       <c r="T19">
-        <v>0.5787675988151733</v>
+        <v>0.5842961691407336</v>
       </c>
       <c r="U19">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>3.698707038117842</v>
+        <v>3.340633215828222</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09575293262896045</v>
+        <v>0.09564598777914642</v>
       </c>
       <c r="C20">
-        <v>78.09860284803959</v>
+        <v>77.47606906817316</v>
       </c>
       <c r="D20">
-        <v>89.24060284803959</v>
+        <v>89.43206906817315</v>
       </c>
       <c r="E20">
-        <v>-12.348</v>
+        <v>-11.534</v>
       </c>
       <c r="F20">
-        <v>14.652</v>
+        <v>15.466</v>
       </c>
       <c r="G20">
         <v>3.51</v>
@@ -2927,28 +2927,28 @@
         <v>3.1375</v>
       </c>
       <c r="M20">
-        <v>0.9391932000000002</v>
+        <v>0.9913706000000001</v>
       </c>
       <c r="N20">
-        <v>2.1983068</v>
+        <v>2.1461294</v>
       </c>
       <c r="O20">
-        <v>0.5495766999999999</v>
+        <v>0.5365323499999999</v>
       </c>
       <c r="P20">
-        <v>1.6487301</v>
+        <v>1.60959705</v>
       </c>
       <c r="Q20">
-        <v>1.6737301</v>
+        <v>1.63459705</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.10621882027922</v>
+        <v>0.1068046145421561</v>
       </c>
       <c r="T20">
-        <v>0.5842961691407336</v>
+        <v>0.5899612473755672</v>
       </c>
       <c r="U20">
         <v>0.0641</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.340633215828223</v>
+        <v>3.164810414995158</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09564598777914642</v>
+        <v>0.09553904292933238</v>
       </c>
       <c r="C21">
-        <v>77.47606906817316</v>
+        <v>76.85435863853428</v>
       </c>
       <c r="D21">
-        <v>89.43206906817315</v>
+        <v>89.62435863853428</v>
       </c>
       <c r="E21">
-        <v>-11.534</v>
+        <v>-10.72</v>
       </c>
       <c r="F21">
-        <v>15.466</v>
+        <v>16.28</v>
       </c>
       <c r="G21">
         <v>3.51</v>
@@ -3009,28 +3009,28 @@
         <v>3.1375</v>
       </c>
       <c r="M21">
-        <v>0.9913706000000001</v>
+        <v>1.043548</v>
       </c>
       <c r="N21">
-        <v>2.1461294</v>
+        <v>2.093952</v>
       </c>
       <c r="O21">
-        <v>0.5365323499999999</v>
+        <v>0.523488</v>
       </c>
       <c r="P21">
-        <v>1.60959705</v>
+        <v>1.570464</v>
       </c>
       <c r="Q21">
-        <v>1.63459705</v>
+        <v>1.595464</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1068046145421561</v>
+        <v>0.1074050536616655</v>
       </c>
       <c r="T21">
-        <v>0.5899612473755672</v>
+        <v>0.5957679525662716</v>
       </c>
       <c r="U21">
         <v>0.0641</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.164810414995158</v>
+        <v>3.006569894245401</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09553904292933238</v>
+        <v>0.09666059807951832</v>
       </c>
       <c r="C22">
-        <v>76.85435863853428</v>
+        <v>74.06400238617556</v>
       </c>
       <c r="D22">
-        <v>89.62435863853428</v>
+        <v>87.64800238617555</v>
       </c>
       <c r="E22">
-        <v>-10.72</v>
+        <v>-9.905999999999999</v>
       </c>
       <c r="F22">
-        <v>16.28</v>
+        <v>17.094</v>
       </c>
       <c r="G22">
         <v>3.51</v>
@@ -3091,45 +3091,45 @@
         <v>3.1375</v>
       </c>
       <c r="M22">
-        <v>1.043548</v>
+        <v>1.2290586</v>
       </c>
       <c r="N22">
-        <v>2.093952</v>
+        <v>1.9084414</v>
       </c>
       <c r="O22">
-        <v>0.523488</v>
+        <v>0.4771103499999999</v>
       </c>
       <c r="P22">
-        <v>1.570464</v>
+        <v>1.43133105</v>
       </c>
       <c r="Q22">
-        <v>1.595464</v>
+        <v>1.45633105</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1074050536616655</v>
+        <v>0.1080206937715422</v>
       </c>
       <c r="T22">
-        <v>0.5957679525662716</v>
+        <v>0.6017216629516773</v>
       </c>
       <c r="U22">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.006569894245401</v>
+        <v>2.552766808677796</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09666059807951832</v>
+        <v>0.09725565322970432</v>
       </c>
       <c r="C23">
-        <v>74.06400238617556</v>
+        <v>72.23640345292364</v>
       </c>
       <c r="D23">
-        <v>87.64800238617555</v>
+        <v>86.63440345292364</v>
       </c>
       <c r="E23">
-        <v>-9.905999999999999</v>
+        <v>-9.091999999999999</v>
       </c>
       <c r="F23">
-        <v>17.094</v>
+        <v>17.908</v>
       </c>
       <c r="G23">
         <v>3.51</v>
@@ -3173,45 +3173,45 @@
         <v>3.1375</v>
       </c>
       <c r="M23">
-        <v>1.2290586</v>
+        <v>1.3574264</v>
       </c>
       <c r="N23">
-        <v>1.9084414</v>
+        <v>1.780073599999999</v>
       </c>
       <c r="O23">
-        <v>0.4771103499999999</v>
+        <v>0.4450183999999999</v>
       </c>
       <c r="P23">
-        <v>1.43133105</v>
+        <v>1.3350552</v>
       </c>
       <c r="Q23">
-        <v>1.45633105</v>
+        <v>1.360055199999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1080206937715422</v>
+        <v>0.1086521195252619</v>
       </c>
       <c r="T23">
-        <v>0.6017216629516773</v>
+        <v>0.6078280325777345</v>
       </c>
       <c r="U23">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V23">
         <v>0.25</v>
       </c>
       <c r="W23">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y23">
-        <v>2.552766808677796</v>
+        <v>2.311359201500721</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09725565322970432</v>
+        <v>0.09723645837989028</v>
       </c>
       <c r="C24">
-        <v>72.23640345292364</v>
+        <v>71.45473332973449</v>
       </c>
       <c r="D24">
-        <v>86.63440345292364</v>
+        <v>86.66673332973448</v>
       </c>
       <c r="E24">
-        <v>-9.091999999999999</v>
+        <v>-8.277999999999999</v>
       </c>
       <c r="F24">
-        <v>17.908</v>
+        <v>18.722</v>
       </c>
       <c r="G24">
         <v>3.51</v>
@@ -3255,28 +3255,28 @@
         <v>3.1375</v>
       </c>
       <c r="M24">
-        <v>1.3574264</v>
+        <v>1.4191276</v>
       </c>
       <c r="N24">
-        <v>1.780073599999999</v>
+        <v>1.7183724</v>
       </c>
       <c r="O24">
-        <v>0.4450183999999999</v>
+        <v>0.4295930999999999</v>
       </c>
       <c r="P24">
-        <v>1.3350552</v>
+        <v>1.2887793</v>
       </c>
       <c r="Q24">
-        <v>1.360055199999999</v>
+        <v>1.3137793</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1086521195252619</v>
+        <v>0.1092999459479095</v>
       </c>
       <c r="T24">
-        <v>0.6078280325777345</v>
+        <v>0.614093009207066</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.311359201500721</v>
+        <v>2.210865323174604</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09723645837989028</v>
+        <v>0.09721726353007626</v>
       </c>
       <c r="C25">
-        <v>71.45473332973449</v>
+        <v>70.67308734501893</v>
       </c>
       <c r="D25">
-        <v>86.66673332973448</v>
+        <v>86.69908734501892</v>
       </c>
       <c r="E25">
-        <v>-8.277999999999999</v>
+        <v>-7.463999999999999</v>
       </c>
       <c r="F25">
-        <v>18.722</v>
+        <v>19.536</v>
       </c>
       <c r="G25">
         <v>3.51</v>
@@ -3337,28 +3337,28 @@
         <v>3.1375</v>
       </c>
       <c r="M25">
-        <v>1.4191276</v>
+        <v>1.4808288</v>
       </c>
       <c r="N25">
-        <v>1.7183724</v>
+        <v>1.656671199999999</v>
       </c>
       <c r="O25">
-        <v>0.4295930999999999</v>
+        <v>0.4141677999999999</v>
       </c>
       <c r="P25">
-        <v>1.2887793</v>
+        <v>1.242503399999999</v>
       </c>
       <c r="Q25">
-        <v>1.3137793</v>
+        <v>1.267503399999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1092999459479095</v>
+        <v>0.1099648204343109</v>
       </c>
       <c r="T25">
-        <v>0.614093009207066</v>
+        <v>0.6205228536424324</v>
       </c>
       <c r="U25">
         <v>0.07580000000000001</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.210865323174604</v>
+        <v>2.118745934708995</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09721726353007626</v>
+        <v>0.09719806868026222</v>
       </c>
       <c r="C26">
-        <v>70.67308734501893</v>
+        <v>69.89146552582091</v>
       </c>
       <c r="D26">
-        <v>86.69908734501892</v>
+        <v>86.73146552582089</v>
       </c>
       <c r="E26">
-        <v>-7.463999999999999</v>
+        <v>-6.649999999999999</v>
       </c>
       <c r="F26">
-        <v>19.536</v>
+        <v>20.35</v>
       </c>
       <c r="G26">
         <v>3.51</v>
@@ -3419,28 +3419,28 @@
         <v>3.1375</v>
       </c>
       <c r="M26">
-        <v>1.4808288</v>
+        <v>1.54253</v>
       </c>
       <c r="N26">
-        <v>1.656671199999999</v>
+        <v>1.59497</v>
       </c>
       <c r="O26">
-        <v>0.4141677999999999</v>
+        <v>0.3987424999999999</v>
       </c>
       <c r="P26">
-        <v>1.242503399999999</v>
+        <v>1.1962275</v>
       </c>
       <c r="Q26">
-        <v>1.267503399999999</v>
+        <v>1.221227499999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1099648204343109</v>
+        <v>0.1106474249070163</v>
       </c>
       <c r="T26">
-        <v>0.6205228536424324</v>
+        <v>0.6271241605960753</v>
       </c>
       <c r="U26">
         <v>0.07580000000000001</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.118745934708995</v>
+        <v>2.033996097320635</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09719806868026222</v>
+        <v>0.09994787383044818</v>
       </c>
       <c r="C27">
-        <v>69.89146552582091</v>
+        <v>64.67295961054027</v>
       </c>
       <c r="D27">
-        <v>86.73146552582089</v>
+        <v>82.32695961054027</v>
       </c>
       <c r="E27">
-        <v>-6.649999999999999</v>
+        <v>-5.835999999999999</v>
       </c>
       <c r="F27">
-        <v>20.35</v>
+        <v>21.164</v>
       </c>
       <c r="G27">
         <v>3.51</v>
@@ -3501,45 +3501,45 @@
         <v>3.1375</v>
       </c>
       <c r="M27">
-        <v>1.54253</v>
+        <v>1.90476</v>
       </c>
       <c r="N27">
-        <v>1.59497</v>
+        <v>1.23274</v>
       </c>
       <c r="O27">
-        <v>0.3987424999999999</v>
+        <v>0.3081849999999999</v>
       </c>
       <c r="P27">
-        <v>1.1962275</v>
+        <v>0.9245549999999998</v>
       </c>
       <c r="Q27">
-        <v>1.221227499999999</v>
+        <v>0.9495549999999998</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1106474249070163</v>
+        <v>0.1113484781492543</v>
       </c>
       <c r="T27">
-        <v>0.6271241605960753</v>
+        <v>0.6339038812511681</v>
       </c>
       <c r="U27">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.033996097320635</v>
+        <v>1.647189147189147</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09994787383044818</v>
+        <v>0.1000351789806341</v>
       </c>
       <c r="C28">
-        <v>64.67295961054027</v>
+        <v>63.72643367980223</v>
       </c>
       <c r="D28">
-        <v>82.32695961054027</v>
+        <v>82.19443367980223</v>
       </c>
       <c r="E28">
-        <v>-5.835999999999999</v>
+        <v>-5.021999999999998</v>
       </c>
       <c r="F28">
-        <v>21.164</v>
+        <v>21.978</v>
       </c>
       <c r="G28">
         <v>3.51</v>
@@ -3583,28 +3583,28 @@
         <v>3.1375</v>
       </c>
       <c r="M28">
-        <v>1.90476</v>
+        <v>1.97802</v>
       </c>
       <c r="N28">
-        <v>1.23274</v>
+        <v>1.15948</v>
       </c>
       <c r="O28">
-        <v>0.3081849999999999</v>
+        <v>0.2898699999999999</v>
       </c>
       <c r="P28">
-        <v>0.9245549999999998</v>
+        <v>0.8696099999999998</v>
       </c>
       <c r="Q28">
-        <v>0.9495549999999998</v>
+        <v>0.8946099999999998</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1113484781492543</v>
+        <v>0.1120687383296358</v>
       </c>
       <c r="T28">
-        <v>0.6339038812511681</v>
+        <v>0.6408693476776333</v>
       </c>
       <c r="U28">
         <v>0.09</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>1.647189147189147</v>
+        <v>1.586182141737697</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1000351789806341</v>
+        <v>0.1001224841308201</v>
       </c>
       <c r="C29">
-        <v>63.72643367980223</v>
+        <v>62.78033373091948</v>
       </c>
       <c r="D29">
-        <v>82.19443367980223</v>
+        <v>82.06233373091948</v>
       </c>
       <c r="E29">
-        <v>-5.021999999999998</v>
+        <v>-4.207999999999995</v>
       </c>
       <c r="F29">
-        <v>21.978</v>
+        <v>22.79200000000001</v>
       </c>
       <c r="G29">
         <v>3.51</v>
@@ -3665,28 +3665,28 @@
         <v>3.1375</v>
       </c>
       <c r="M29">
-        <v>1.97802</v>
+        <v>2.05128</v>
       </c>
       <c r="N29">
-        <v>1.15948</v>
+        <v>1.08622</v>
       </c>
       <c r="O29">
-        <v>0.2898699999999999</v>
+        <v>0.2715549999999999</v>
       </c>
       <c r="P29">
-        <v>0.8696099999999998</v>
+        <v>0.8146649999999996</v>
       </c>
       <c r="Q29">
-        <v>0.8946099999999998</v>
+        <v>0.8396649999999997</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1120687383296358</v>
+        <v>0.1128090057372502</v>
       </c>
       <c r="T29">
-        <v>0.6408693476776333</v>
+        <v>0.6480282992826112</v>
       </c>
       <c r="U29">
         <v>0.09</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.586182141737697</v>
+        <v>1.529532779532779</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1001224841308201</v>
+        <v>0.113926578504472</v>
       </c>
       <c r="C30">
-        <v>62.78033373091948</v>
+        <v>45.33851791789766</v>
       </c>
       <c r="D30">
-        <v>82.06233373091948</v>
+        <v>65.43451791789767</v>
       </c>
       <c r="E30">
-        <v>-4.207999999999995</v>
+        <v>-3.393999999999995</v>
       </c>
       <c r="F30">
-        <v>22.79200000000001</v>
+        <v>23.60600000000001</v>
       </c>
       <c r="G30">
         <v>3.51</v>
@@ -3747,45 +3747,45 @@
         <v>3.1375</v>
       </c>
       <c r="M30">
-        <v>2.05128</v>
+        <v>3.465360800000001</v>
       </c>
       <c r="N30">
-        <v>1.08622</v>
+        <v>-0.3278608000000012</v>
       </c>
       <c r="O30">
-        <v>0.2715549999999999</v>
+        <v>-0.08196520000000029</v>
       </c>
       <c r="P30">
-        <v>0.8146649999999996</v>
+        <v>-0.2458956000000009</v>
       </c>
       <c r="Q30">
-        <v>0.8396649999999997</v>
+        <v>-0.2208956000000009</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1128090057372502</v>
+        <v>0.1140713169232796</v>
       </c>
       <c r="T30">
-        <v>0.6480282992826112</v>
+        <v>0.6602358132137329</v>
       </c>
       <c r="U30">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.25</v>
+        <v>0.2263472825109581</v>
       </c>
       <c r="W30">
-        <v>0.0675</v>
+        <v>0.1135722189273914</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.529532779532779</v>
+        <v>0.9053891300438324</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.113926578504472</v>
+        <v>0.114936578504472</v>
       </c>
       <c r="C31">
-        <v>45.33851791789768</v>
+        <v>43.56860044950861</v>
       </c>
       <c r="D31">
-        <v>65.43451791789768</v>
+        <v>64.4786004495086</v>
       </c>
       <c r="E31">
-        <v>-3.393999999999998</v>
+        <v>-2.579999999999998</v>
       </c>
       <c r="F31">
-        <v>23.606</v>
+        <v>24.42</v>
       </c>
       <c r="G31">
         <v>3.51</v>
@@ -3829,37 +3829,37 @@
         <v>3.1375</v>
       </c>
       <c r="M31">
-        <v>3.4653608</v>
+        <v>3.584856000000001</v>
       </c>
       <c r="N31">
-        <v>-0.3278608000000007</v>
+        <v>-0.447356000000001</v>
       </c>
       <c r="O31">
-        <v>-0.08196520000000018</v>
+        <v>-0.1118390000000002</v>
       </c>
       <c r="P31">
-        <v>-0.2458956000000005</v>
+        <v>-0.3355170000000007</v>
       </c>
       <c r="Q31">
-        <v>-0.2208956000000006</v>
+        <v>-0.3105170000000007</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1140713169232796</v>
+        <v>0.1150466214507551</v>
       </c>
       <c r="T31">
-        <v>0.6602358132137329</v>
+        <v>0.6696677534025006</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.2263472825109581</v>
+        <v>0.2188023730939262</v>
       </c>
       <c r="W31">
-        <v>0.1135722189273914</v>
+        <v>0.1146798116298117</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.9053891300438325</v>
+        <v>0.8752094923757047</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.114936578504472</v>
+        <v>0.115946578504472</v>
       </c>
       <c r="C32">
-        <v>43.56860044950861</v>
+        <v>41.8262103862662</v>
       </c>
       <c r="D32">
-        <v>64.4786004495086</v>
+        <v>63.55021038626621</v>
       </c>
       <c r="E32">
-        <v>-2.579999999999998</v>
+        <v>-1.765999999999998</v>
       </c>
       <c r="F32">
-        <v>24.42</v>
+        <v>25.234</v>
       </c>
       <c r="G32">
         <v>3.51</v>
@@ -3911,37 +3911,37 @@
         <v>3.1375</v>
       </c>
       <c r="M32">
-        <v>3.584856000000001</v>
+        <v>3.704351200000001</v>
       </c>
       <c r="N32">
-        <v>-0.447356000000001</v>
+        <v>-0.5668512000000008</v>
       </c>
       <c r="O32">
-        <v>-0.1118390000000002</v>
+        <v>-0.1417128000000002</v>
       </c>
       <c r="P32">
-        <v>-0.3355170000000007</v>
+        <v>-0.4251384000000006</v>
       </c>
       <c r="Q32">
-        <v>-0.3105170000000007</v>
+        <v>-0.4001384000000006</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1150466214507551</v>
+        <v>0.1160501956746791</v>
       </c>
       <c r="T32">
-        <v>0.6696677534025006</v>
+        <v>0.6793730831619571</v>
       </c>
       <c r="U32">
         <v>0.1468</v>
       </c>
       <c r="V32">
-        <v>0.2188023730939262</v>
+        <v>0.2117442320263802</v>
       </c>
       <c r="W32">
-        <v>0.1146798116298117</v>
+        <v>0.1157159467385274</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.8752094923757047</v>
+        <v>0.8469769281055207</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.115946578504472</v>
+        <v>0.116956578504472</v>
       </c>
       <c r="C33">
-        <v>41.8262103862662</v>
+        <v>40.11017555211389</v>
       </c>
       <c r="D33">
-        <v>63.55021038626621</v>
+        <v>62.64817555211388</v>
       </c>
       <c r="E33">
-        <v>-1.765999999999998</v>
+        <v>-0.9519999999999982</v>
       </c>
       <c r="F33">
-        <v>25.234</v>
+        <v>26.048</v>
       </c>
       <c r="G33">
         <v>3.51</v>
@@ -3993,37 +3993,37 @@
         <v>3.1375</v>
       </c>
       <c r="M33">
-        <v>3.704351200000001</v>
+        <v>3.823846400000001</v>
       </c>
       <c r="N33">
-        <v>-0.5668512000000008</v>
+        <v>-0.686346400000001</v>
       </c>
       <c r="O33">
-        <v>-0.1417128000000002</v>
+        <v>-0.1715866000000003</v>
       </c>
       <c r="P33">
-        <v>-0.4251384000000006</v>
+        <v>-0.5147598000000008</v>
       </c>
       <c r="Q33">
-        <v>-0.4001384000000006</v>
+        <v>-0.4897598000000007</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1160501956746791</v>
+        <v>0.117083286787542</v>
       </c>
       <c r="T33">
-        <v>0.6793730831619571</v>
+        <v>0.6893638637966919</v>
       </c>
       <c r="U33">
         <v>0.1468</v>
       </c>
       <c r="V33">
-        <v>0.2117442320263802</v>
+        <v>0.2051272247755558</v>
       </c>
       <c r="W33">
-        <v>0.1157159467385274</v>
+        <v>0.1166873234029484</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.8469769281055207</v>
+        <v>0.8205088991022231</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.116956578504472</v>
+        <v>0.1367023477531999</v>
       </c>
       <c r="C34">
-        <v>40.11017555211389</v>
+        <v>25.68776555081893</v>
       </c>
       <c r="D34">
-        <v>62.64817555211388</v>
+        <v>49.03976555081893</v>
       </c>
       <c r="E34">
-        <v>-0.9519999999999982</v>
+        <v>-0.1379999999999981</v>
       </c>
       <c r="F34">
-        <v>26.048</v>
+        <v>26.862</v>
       </c>
       <c r="G34">
         <v>3.51</v>
@@ -4075,45 +4075,45 @@
         <v>3.1375</v>
       </c>
       <c r="M34">
-        <v>3.823846400000001</v>
+        <v>5.393889600000001</v>
       </c>
       <c r="N34">
-        <v>-0.686346400000001</v>
+        <v>-2.256389600000001</v>
       </c>
       <c r="O34">
-        <v>-0.1715866000000003</v>
+        <v>-0.5640974000000002</v>
       </c>
       <c r="P34">
-        <v>-0.5147598000000008</v>
+        <v>-1.692292200000001</v>
       </c>
       <c r="Q34">
-        <v>-0.4897598000000007</v>
+        <v>-1.667292200000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.117083286787542</v>
+        <v>0.1195140362153081</v>
       </c>
       <c r="T34">
-        <v>0.6893638637966919</v>
+        <v>0.7128710685421852</v>
       </c>
       <c r="U34">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.2051272247755558</v>
+        <v>0.1454191795100886</v>
       </c>
       <c r="W34">
-        <v>0.1166873234029484</v>
+        <v>0.1715998287543742</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y34">
-        <v>0.8205088991022231</v>
+        <v>0.5816767180403544</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1367023477531999</v>
+        <v>0.1382523477531999</v>
       </c>
       <c r="C35">
-        <v>25.68776555081893</v>
+        <v>24.05159457895048</v>
       </c>
       <c r="D35">
-        <v>49.03976555081893</v>
+        <v>48.21759457895049</v>
       </c>
       <c r="E35">
-        <v>-0.1379999999999981</v>
+        <v>0.6760000000000055</v>
       </c>
       <c r="F35">
-        <v>26.862</v>
+        <v>27.67600000000001</v>
       </c>
       <c r="G35">
         <v>3.51</v>
@@ -4157,37 +4157,37 @@
         <v>3.1375</v>
       </c>
       <c r="M35">
-        <v>5.393889600000001</v>
+        <v>5.557340800000001</v>
       </c>
       <c r="N35">
-        <v>-2.256389600000001</v>
+        <v>-2.419840800000002</v>
       </c>
       <c r="O35">
-        <v>-0.5640974000000002</v>
+        <v>-0.6049602000000004</v>
       </c>
       <c r="P35">
-        <v>-1.692292200000001</v>
+        <v>-1.814880600000001</v>
       </c>
       <c r="Q35">
-        <v>-1.667292200000001</v>
+        <v>-1.789880600000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1195140362153081</v>
+        <v>0.1206309155519037</v>
       </c>
       <c r="T35">
-        <v>0.7128710685421852</v>
+        <v>0.7236721453382788</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1454191795100886</v>
+        <v>0.1411421448186154</v>
       </c>
       <c r="W35">
-        <v>0.1715998287543742</v>
+        <v>0.172458657320422</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5816767180403544</v>
+        <v>0.5645685792744615</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1382523477531999</v>
+        <v>0.1398023477531999</v>
       </c>
       <c r="C36">
-        <v>24.05159457895048</v>
+        <v>22.44253707896553</v>
       </c>
       <c r="D36">
-        <v>48.21759457895049</v>
+        <v>47.42253707896554</v>
       </c>
       <c r="E36">
-        <v>0.6760000000000055</v>
+        <v>1.490000000000006</v>
       </c>
       <c r="F36">
-        <v>27.67600000000001</v>
+        <v>28.49000000000001</v>
       </c>
       <c r="G36">
         <v>3.51</v>
@@ -4239,37 +4239,37 @@
         <v>3.1375</v>
       </c>
       <c r="M36">
-        <v>5.557340800000001</v>
+        <v>5.720792000000001</v>
       </c>
       <c r="N36">
-        <v>-2.419840800000002</v>
+        <v>-2.583292000000001</v>
       </c>
       <c r="O36">
-        <v>-0.6049602000000004</v>
+        <v>-0.6458230000000004</v>
       </c>
       <c r="P36">
-        <v>-1.814880600000001</v>
+        <v>-1.937469000000001</v>
       </c>
       <c r="Q36">
-        <v>-1.789880600000001</v>
+        <v>-1.912469000000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1206309155519037</v>
+        <v>0.1217821604065484</v>
       </c>
       <c r="T36">
-        <v>0.7236721453382788</v>
+        <v>0.7348055629588678</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1411421448186154</v>
+        <v>0.1371095121095121</v>
       </c>
       <c r="W36">
-        <v>0.172458657320422</v>
+        <v>0.17326840996841</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5645685792744615</v>
+        <v>0.5484380484380482</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1398023477531999</v>
+        <v>0.1413523477531999</v>
       </c>
       <c r="C37">
-        <v>22.44253707896553</v>
+        <v>20.85927358936242</v>
       </c>
       <c r="D37">
-        <v>47.42253707896554</v>
+        <v>46.65327358936243</v>
       </c>
       <c r="E37">
-        <v>1.490000000000006</v>
+        <v>2.304000000000006</v>
       </c>
       <c r="F37">
-        <v>28.49000000000001</v>
+        <v>29.30400000000001</v>
       </c>
       <c r="G37">
         <v>3.51</v>
@@ -4321,37 +4321,37 @@
         <v>3.1375</v>
       </c>
       <c r="M37">
-        <v>5.720792000000001</v>
+        <v>5.884243200000001</v>
       </c>
       <c r="N37">
-        <v>-2.583292000000001</v>
+        <v>-2.746743200000001</v>
       </c>
       <c r="O37">
-        <v>-0.6458230000000004</v>
+        <v>-0.6866858000000003</v>
       </c>
       <c r="P37">
-        <v>-1.937469000000001</v>
+        <v>-2.060057400000001</v>
       </c>
       <c r="Q37">
-        <v>-1.912469000000001</v>
+        <v>-2.035057400000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1217821604065484</v>
+        <v>0.1229693816629007</v>
       </c>
       <c r="T37">
-        <v>0.7348055629588678</v>
+        <v>0.7462868998801001</v>
       </c>
       <c r="U37">
         <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1371095121095121</v>
+        <v>0.1333009145509145</v>
       </c>
       <c r="W37">
-        <v>0.17326840996841</v>
+        <v>0.1740331763581764</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.5484380484380482</v>
+        <v>0.5332036582036581</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1413523477531999</v>
+        <v>0.1429023477531999</v>
       </c>
       <c r="C38">
-        <v>20.85927358936242</v>
+        <v>19.30056889646144</v>
       </c>
       <c r="D38">
-        <v>46.65327358936243</v>
+        <v>45.90856889646144</v>
       </c>
       <c r="E38">
-        <v>2.304000000000002</v>
+        <v>3.118000000000002</v>
       </c>
       <c r="F38">
-        <v>29.304</v>
+        <v>30.118</v>
       </c>
       <c r="G38">
         <v>3.51</v>
@@ -4403,37 +4403,37 @@
         <v>3.1375</v>
       </c>
       <c r="M38">
-        <v>5.8842432</v>
+        <v>6.047694400000001</v>
       </c>
       <c r="N38">
-        <v>-2.7467432</v>
+        <v>-2.910194400000001</v>
       </c>
       <c r="O38">
-        <v>-0.6866858000000001</v>
+        <v>-0.7275486000000003</v>
       </c>
       <c r="P38">
-        <v>-2.0600574</v>
+        <v>-2.182645800000001</v>
       </c>
       <c r="Q38">
-        <v>-2.0350574</v>
+        <v>-2.157645800000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1229693816629007</v>
+        <v>0.1241942924829467</v>
       </c>
       <c r="T38">
-        <v>0.7462868998801001</v>
+        <v>0.7581327236877206</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.1333009145509145</v>
+        <v>0.1296981871306195</v>
       </c>
       <c r="W38">
-        <v>0.1740331763581764</v>
+        <v>0.1747566040241716</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.5332036582036581</v>
+        <v>0.5187927485224781</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1429023477531999</v>
+        <v>0.1444523477532</v>
       </c>
       <c r="C39">
-        <v>19.30056889646144</v>
+        <v>17.76526541600567</v>
       </c>
       <c r="D39">
-        <v>45.90856889646144</v>
+        <v>45.18726541600567</v>
       </c>
       <c r="E39">
-        <v>3.118000000000002</v>
+        <v>3.932000000000002</v>
       </c>
       <c r="F39">
-        <v>30.118</v>
+        <v>30.932</v>
       </c>
       <c r="G39">
         <v>3.51</v>
@@ -4485,37 +4485,37 @@
         <v>3.1375</v>
       </c>
       <c r="M39">
-        <v>6.047694400000001</v>
+        <v>6.211145600000001</v>
       </c>
       <c r="N39">
-        <v>-2.910194400000001</v>
+        <v>-3.073645600000001</v>
       </c>
       <c r="O39">
-        <v>-0.7275486000000003</v>
+        <v>-0.7684114000000003</v>
       </c>
       <c r="P39">
-        <v>-2.182645800000001</v>
+        <v>-2.305234200000001</v>
       </c>
       <c r="Q39">
-        <v>-2.157645800000001</v>
+        <v>-2.280234200000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1241942924829467</v>
+        <v>0.1254587165552523</v>
       </c>
       <c r="T39">
-        <v>0.7581327236877206</v>
+        <v>0.7703606708439743</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.1296981871306195</v>
+        <v>0.1262850769429716</v>
       </c>
       <c r="W39">
-        <v>0.1747566040241716</v>
+        <v>0.1754419565498513</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5187927485224781</v>
+        <v>0.5051403077718866</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1444523477532</v>
+        <v>0.1600218717063275</v>
       </c>
       <c r="C40">
-        <v>17.76526541600567</v>
+        <v>10.7918127581146</v>
       </c>
       <c r="D40">
-        <v>45.18726541600567</v>
+        <v>39.0278127581146</v>
       </c>
       <c r="E40">
-        <v>3.932000000000002</v>
+        <v>4.746000000000002</v>
       </c>
       <c r="F40">
-        <v>30.932</v>
+        <v>31.746</v>
       </c>
       <c r="G40">
         <v>3.51</v>
@@ -4567,45 +4567,45 @@
         <v>3.1375</v>
       </c>
       <c r="M40">
-        <v>6.211145600000001</v>
+        <v>7.485706800000001</v>
       </c>
       <c r="N40">
-        <v>-3.073645600000001</v>
+        <v>-4.348206800000002</v>
       </c>
       <c r="O40">
-        <v>-0.7684114000000003</v>
+        <v>-1.0870517</v>
       </c>
       <c r="P40">
-        <v>-2.305234200000001</v>
+        <v>-3.261155100000001</v>
       </c>
       <c r="Q40">
-        <v>-2.280234200000001</v>
+        <v>-3.236155100000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1254587165552523</v>
+        <v>0.127370374126859</v>
       </c>
       <c r="T40">
-        <v>0.7703606708439743</v>
+        <v>0.7888478606076387</v>
       </c>
       <c r="U40">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.1262850769429716</v>
+        <v>0.1047830246303529</v>
       </c>
       <c r="W40">
-        <v>0.1754419565498513</v>
+        <v>0.2110921627921628</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y40">
-        <v>0.5051403077718866</v>
+        <v>0.4191320985214113</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1600218717063275</v>
+        <v>0.1619218717063275</v>
       </c>
       <c r="C41">
-        <v>10.7918127581146</v>
+        <v>9.339235002255208</v>
       </c>
       <c r="D41">
-        <v>39.0278127581146</v>
+        <v>38.38923500225521</v>
       </c>
       <c r="E41">
-        <v>4.746000000000002</v>
+        <v>5.560000000000002</v>
       </c>
       <c r="F41">
-        <v>31.746</v>
+        <v>32.56</v>
       </c>
       <c r="G41">
         <v>3.51</v>
@@ -4649,37 +4649,37 @@
         <v>3.1375</v>
       </c>
       <c r="M41">
-        <v>7.485706800000001</v>
+        <v>7.677648</v>
       </c>
       <c r="N41">
-        <v>-4.348206800000002</v>
+        <v>-4.540148</v>
       </c>
       <c r="O41">
-        <v>-1.0870517</v>
+        <v>-1.135037</v>
       </c>
       <c r="P41">
-        <v>-3.261155100000001</v>
+        <v>-3.405111</v>
       </c>
       <c r="Q41">
-        <v>-3.236155100000001</v>
+        <v>-3.380111</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.127370374126859</v>
+        <v>0.1287298803623067</v>
       </c>
       <c r="T41">
-        <v>0.7888478606076387</v>
+        <v>0.8019953249510993</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.1047830246303529</v>
+        <v>0.102163449014594</v>
       </c>
       <c r="W41">
-        <v>0.2110921627921628</v>
+        <v>0.2117098587223587</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.4191320985214113</v>
+        <v>0.4086537960583763</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1619218717063275</v>
+        <v>0.1638218717063275</v>
       </c>
       <c r="C42">
-        <v>9.339235002255208</v>
+        <v>7.90721780383474</v>
       </c>
       <c r="D42">
-        <v>38.38923500225521</v>
+        <v>37.77121780383474</v>
       </c>
       <c r="E42">
-        <v>5.560000000000002</v>
+        <v>6.374000000000002</v>
       </c>
       <c r="F42">
-        <v>32.56</v>
+        <v>33.374</v>
       </c>
       <c r="G42">
         <v>3.51</v>
@@ -4731,37 +4731,37 @@
         <v>3.1375</v>
       </c>
       <c r="M42">
-        <v>7.677648</v>
+        <v>7.869589200000001</v>
       </c>
       <c r="N42">
-        <v>-4.540148</v>
+        <v>-4.732089200000001</v>
       </c>
       <c r="O42">
-        <v>-1.135037</v>
+        <v>-1.1830223</v>
       </c>
       <c r="P42">
-        <v>-3.405111</v>
+        <v>-3.549066900000001</v>
       </c>
       <c r="Q42">
-        <v>-3.380111</v>
+        <v>-3.524066900000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1287298803623067</v>
+        <v>0.1301354715548882</v>
       </c>
       <c r="T42">
-        <v>0.8019953249510993</v>
+        <v>0.8155884660519654</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.102163449014594</v>
+        <v>0.09967165757521369</v>
       </c>
       <c r="W42">
-        <v>0.2117098587223587</v>
+        <v>0.2122974231437646</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4086537960583763</v>
+        <v>0.3986866303008548</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1638218717063275</v>
+        <v>0.1657218717063275</v>
       </c>
       <c r="C43">
-        <v>7.90721780383474</v>
+        <v>6.494783900109233</v>
       </c>
       <c r="D43">
-        <v>37.77121780383474</v>
+        <v>37.17278390010924</v>
       </c>
       <c r="E43">
-        <v>6.374000000000002</v>
+        <v>7.188000000000002</v>
       </c>
       <c r="F43">
-        <v>33.374</v>
+        <v>34.188</v>
       </c>
       <c r="G43">
         <v>3.51</v>
@@ -4813,37 +4813,37 @@
         <v>3.1375</v>
       </c>
       <c r="M43">
-        <v>7.869589200000001</v>
+        <v>8.061530400000001</v>
       </c>
       <c r="N43">
-        <v>-4.732089200000001</v>
+        <v>-4.924030400000001</v>
       </c>
       <c r="O43">
-        <v>-1.1830223</v>
+        <v>-1.2310076</v>
       </c>
       <c r="P43">
-        <v>-3.549066900000001</v>
+        <v>-3.693022800000001</v>
       </c>
       <c r="Q43">
-        <v>-3.524066900000001</v>
+        <v>-3.668022800000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1301354715548882</v>
+        <v>0.1315895314092828</v>
       </c>
       <c r="T43">
-        <v>0.8155884660519654</v>
+        <v>0.8296503361563096</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.09967165757521369</v>
+        <v>0.09729852287104195</v>
       </c>
       <c r="W43">
-        <v>0.2122974231437646</v>
+        <v>0.2128570083070083</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3986866303008548</v>
+        <v>0.3891940914841677</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1657218717063275</v>
+        <v>0.1676218717063275</v>
       </c>
       <c r="C44">
-        <v>6.494783900109233</v>
+        <v>5.101016996014458</v>
       </c>
       <c r="D44">
-        <v>37.17278390010924</v>
+        <v>36.59301699601446</v>
       </c>
       <c r="E44">
-        <v>7.188000000000002</v>
+        <v>8.002000000000002</v>
       </c>
       <c r="F44">
-        <v>34.188</v>
+        <v>35.002</v>
       </c>
       <c r="G44">
         <v>3.51</v>
@@ -4895,37 +4895,37 @@
         <v>3.1375</v>
       </c>
       <c r="M44">
-        <v>8.061530400000001</v>
+        <v>8.253471600000001</v>
       </c>
       <c r="N44">
-        <v>-4.924030400000001</v>
+        <v>-5.115971600000002</v>
       </c>
       <c r="O44">
-        <v>-1.2310076</v>
+        <v>-1.2789929</v>
       </c>
       <c r="P44">
-        <v>-3.693022800000001</v>
+        <v>-3.836978700000001</v>
       </c>
       <c r="Q44">
-        <v>-3.668022800000001</v>
+        <v>-3.811978700000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1315895314092828</v>
+        <v>0.1330946109076912</v>
       </c>
       <c r="T44">
-        <v>0.8296503361563096</v>
+        <v>0.8442056052116834</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.09729852287104195</v>
+        <v>0.09503576652520375</v>
       </c>
       <c r="W44">
-        <v>0.2128570083070083</v>
+        <v>0.213390566253357</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3891940914841677</v>
+        <v>0.3801430661008149</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1676218717063275</v>
+        <v>0.1695218717063275</v>
       </c>
       <c r="C45">
-        <v>5.101016996014458</v>
+        <v>3.725057082754674</v>
       </c>
       <c r="D45">
-        <v>36.59301699601446</v>
+        <v>36.03105708275468</v>
       </c>
       <c r="E45">
-        <v>8.002000000000002</v>
+        <v>8.816000000000003</v>
       </c>
       <c r="F45">
-        <v>35.002</v>
+        <v>35.816</v>
       </c>
       <c r="G45">
         <v>3.51</v>
@@ -4977,37 +4977,37 @@
         <v>3.1375</v>
       </c>
       <c r="M45">
-        <v>8.253471600000001</v>
+        <v>8.445412800000001</v>
       </c>
       <c r="N45">
-        <v>-5.115971600000002</v>
+        <v>-5.307912800000002</v>
       </c>
       <c r="O45">
-        <v>-1.2789929</v>
+        <v>-1.326978200000001</v>
       </c>
       <c r="P45">
-        <v>-3.836978700000001</v>
+        <v>-3.980934600000002</v>
       </c>
       <c r="Q45">
-        <v>-3.811978700000001</v>
+        <v>-3.955934600000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1330946109076912</v>
+        <v>0.1346534432453286</v>
       </c>
       <c r="T45">
-        <v>0.8442056052116834</v>
+        <v>0.8592807053047493</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.09503576652520375</v>
+        <v>0.09287586274054002</v>
       </c>
       <c r="W45">
-        <v>0.213390566253357</v>
+        <v>0.2138998715657807</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3801430661008149</v>
+        <v>0.3715034509621601</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1695218717063275</v>
+        <v>0.1714218717063275</v>
       </c>
       <c r="C46">
-        <v>3.725057082754674</v>
+        <v>2.366096181222545</v>
       </c>
       <c r="D46">
-        <v>36.03105708275468</v>
+        <v>35.48609618122255</v>
       </c>
       <c r="E46">
-        <v>8.816000000000003</v>
+        <v>9.630000000000003</v>
       </c>
       <c r="F46">
-        <v>35.816</v>
+        <v>36.63</v>
       </c>
       <c r="G46">
         <v>3.51</v>
@@ -5059,37 +5059,37 @@
         <v>3.1375</v>
       </c>
       <c r="M46">
-        <v>8.445412800000001</v>
+        <v>8.637354</v>
       </c>
       <c r="N46">
-        <v>-5.307912800000002</v>
+        <v>-5.499854000000001</v>
       </c>
       <c r="O46">
-        <v>-1.326978200000001</v>
+        <v>-1.3749635</v>
       </c>
       <c r="P46">
-        <v>-3.980934600000002</v>
+        <v>-4.124890500000001</v>
       </c>
       <c r="Q46">
-        <v>-3.955934600000002</v>
+        <v>-4.099890500000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1346534432453286</v>
+        <v>0.1362689603952436</v>
       </c>
       <c r="T46">
-        <v>0.8592807053047493</v>
+        <v>0.8749039908557447</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.09287586274054002</v>
+        <v>0.09081195467963915</v>
       </c>
       <c r="W46">
-        <v>0.2138998715657807</v>
+        <v>0.2143865410865411</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3715034509621601</v>
+        <v>0.3632478187185565</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1714218717063275</v>
+        <v>0.1733218717063275</v>
       </c>
       <c r="C47">
-        <v>2.366096181222545</v>
+        <v>1.023374465942247</v>
       </c>
       <c r="D47">
-        <v>35.48609618122255</v>
+        <v>34.95737446594225</v>
       </c>
       <c r="E47">
-        <v>9.630000000000003</v>
+        <v>10.444</v>
       </c>
       <c r="F47">
-        <v>36.63</v>
+        <v>37.444</v>
       </c>
       <c r="G47">
         <v>3.51</v>
@@ -5141,37 +5141,37 @@
         <v>3.1375</v>
       </c>
       <c r="M47">
-        <v>8.637354</v>
+        <v>8.829295200000001</v>
       </c>
       <c r="N47">
-        <v>-5.499854000000001</v>
+        <v>-5.691795200000001</v>
       </c>
       <c r="O47">
-        <v>-1.3749635</v>
+        <v>-1.4229488</v>
       </c>
       <c r="P47">
-        <v>-4.124890500000001</v>
+        <v>-4.268846400000001</v>
       </c>
       <c r="Q47">
-        <v>-4.099890500000001</v>
+        <v>-4.243846400000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1362689603952436</v>
+        <v>0.1379443115136741</v>
       </c>
       <c r="T47">
-        <v>0.8749039908557447</v>
+        <v>0.8911059166123325</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.09081195467963915</v>
+        <v>0.0888377817518209</v>
       </c>
       <c r="W47">
-        <v>0.2143865410865411</v>
+        <v>0.2148520510629207</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3632478187185565</v>
+        <v>0.3553511270072836</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1733218717063275</v>
+        <v>0.1752218717063275</v>
       </c>
       <c r="C48">
-        <v>1.023374465942247</v>
+        <v>-0.3038232695688166</v>
       </c>
       <c r="D48">
-        <v>34.95737446594225</v>
+        <v>34.44417673043119</v>
       </c>
       <c r="E48">
-        <v>10.444</v>
+        <v>11.258</v>
       </c>
       <c r="F48">
-        <v>37.444</v>
+        <v>38.258</v>
       </c>
       <c r="G48">
         <v>3.51</v>
@@ -5223,37 +5223,37 @@
         <v>3.1375</v>
       </c>
       <c r="M48">
-        <v>8.829295200000001</v>
+        <v>9.021236400000001</v>
       </c>
       <c r="N48">
-        <v>-5.691795200000001</v>
+        <v>-5.883736400000002</v>
       </c>
       <c r="O48">
-        <v>-1.4229488</v>
+        <v>-1.4709341</v>
       </c>
       <c r="P48">
-        <v>-4.268846400000001</v>
+        <v>-4.412802300000001</v>
       </c>
       <c r="Q48">
-        <v>-4.243846400000001</v>
+        <v>-4.387802300000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1379443115136741</v>
+        <v>0.1396828834290264</v>
       </c>
       <c r="T48">
-        <v>0.8911059166123325</v>
+        <v>0.9079192357936973</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.0888377817518209</v>
+        <v>0.08694761618263322</v>
       </c>
       <c r="W48">
-        <v>0.2148520510629207</v>
+        <v>0.2152977521041351</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3553511270072836</v>
+        <v>0.3477904647305329</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1752218717063275</v>
+        <v>0.1771218717063275</v>
       </c>
       <c r="C49">
-        <v>-0.3038232695688166</v>
+        <v>-1.616170840597732</v>
       </c>
       <c r="D49">
-        <v>34.44417673043119</v>
+        <v>33.94582915940227</v>
       </c>
       <c r="E49">
-        <v>11.258</v>
+        <v>12.072</v>
       </c>
       <c r="F49">
-        <v>38.258</v>
+        <v>39.072</v>
       </c>
       <c r="G49">
         <v>3.51</v>
@@ -5305,37 +5305,37 @@
         <v>3.1375</v>
       </c>
       <c r="M49">
-        <v>9.021236400000001</v>
+        <v>9.213177600000002</v>
       </c>
       <c r="N49">
-        <v>-5.883736400000002</v>
+        <v>-6.075677600000002</v>
       </c>
       <c r="O49">
-        <v>-1.4709341</v>
+        <v>-1.518919400000001</v>
       </c>
       <c r="P49">
-        <v>-4.412802300000001</v>
+        <v>-4.556758200000002</v>
       </c>
       <c r="Q49">
-        <v>-4.387802300000001</v>
+        <v>-4.531758200000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1396828834290264</v>
+        <v>0.1414883234949692</v>
       </c>
       <c r="T49">
-        <v>0.9079192357936973</v>
+        <v>0.9253792210974222</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08694761618263322</v>
+        <v>0.08513620751216169</v>
       </c>
       <c r="W49">
-        <v>0.2152977521041351</v>
+        <v>0.2157248822686323</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3477904647305329</v>
+        <v>0.3405448300486467</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1771218717063275</v>
+        <v>0.1790218717063275</v>
       </c>
       <c r="C50">
-        <v>-1.616170840597725</v>
+        <v>-2.914303622826161</v>
       </c>
       <c r="D50">
-        <v>33.94582915940228</v>
+        <v>33.46169637717384</v>
       </c>
       <c r="E50">
-        <v>12.072</v>
+        <v>12.886</v>
       </c>
       <c r="F50">
-        <v>39.072</v>
+        <v>39.886</v>
       </c>
       <c r="G50">
         <v>3.51</v>
@@ -5387,37 +5387,37 @@
         <v>3.1375</v>
       </c>
       <c r="M50">
-        <v>9.213177600000002</v>
+        <v>9.4051188</v>
       </c>
       <c r="N50">
-        <v>-6.075677600000002</v>
+        <v>-6.267618800000001</v>
       </c>
       <c r="O50">
-        <v>-1.518919400000001</v>
+        <v>-1.5669047</v>
       </c>
       <c r="P50">
-        <v>-4.556758200000002</v>
+        <v>-4.700714100000001</v>
       </c>
       <c r="Q50">
-        <v>-4.531758200000001</v>
+        <v>-4.6757141</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1414883234949692</v>
+        <v>0.1433645651321255</v>
       </c>
       <c r="T50">
-        <v>0.9253792210974221</v>
+        <v>0.9435239117071755</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.08513620751216169</v>
+        <v>0.08339873388946452</v>
       </c>
       <c r="W50">
-        <v>0.2157248822686323</v>
+        <v>0.2161345785488643</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3405448300486467</v>
+        <v>0.333594935557858</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1790218717063275</v>
+        <v>0.1809218717063275</v>
       </c>
       <c r="C51">
-        <v>-2.914303622826161</v>
+        <v>-4.198821254899883</v>
       </c>
       <c r="D51">
-        <v>33.46169637717384</v>
+        <v>32.99117874510012</v>
       </c>
       <c r="E51">
-        <v>12.886</v>
+        <v>13.7</v>
       </c>
       <c r="F51">
-        <v>39.886</v>
+        <v>40.7</v>
       </c>
       <c r="G51">
         <v>3.51</v>
@@ -5469,37 +5469,37 @@
         <v>3.1375</v>
       </c>
       <c r="M51">
-        <v>9.4051188</v>
+        <v>9.597060000000001</v>
       </c>
       <c r="N51">
-        <v>-6.267618800000001</v>
+        <v>-6.459560000000002</v>
       </c>
       <c r="O51">
-        <v>-1.5669047</v>
+        <v>-1.61489</v>
       </c>
       <c r="P51">
-        <v>-4.700714100000001</v>
+        <v>-4.844670000000001</v>
       </c>
       <c r="Q51">
-        <v>-4.6757141</v>
+        <v>-4.81967</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1433645651321255</v>
+        <v>0.145315856434768</v>
       </c>
       <c r="T51">
-        <v>0.9435239117071755</v>
+        <v>0.9623943899413192</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.08339873388946452</v>
+        <v>0.08173075921167523</v>
       </c>
       <c r="W51">
-        <v>0.2161345785488643</v>
+        <v>0.216527886977887</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.333594935557858</v>
+        <v>0.3269230368467009</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1809218717063275</v>
+        <v>0.1828218717063275</v>
       </c>
       <c r="C52">
-        <v>-4.198821254899883</v>
+        <v>-5.470290116148817</v>
       </c>
       <c r="D52">
-        <v>32.99117874510012</v>
+        <v>32.53370988385119</v>
       </c>
       <c r="E52">
-        <v>13.7</v>
+        <v>14.514</v>
       </c>
       <c r="F52">
-        <v>40.7</v>
+        <v>41.514</v>
       </c>
       <c r="G52">
         <v>3.51</v>
@@ -5551,37 +5551,37 @@
         <v>3.1375</v>
       </c>
       <c r="M52">
-        <v>9.597060000000001</v>
+        <v>9.789001200000001</v>
       </c>
       <c r="N52">
-        <v>-6.459560000000002</v>
+        <v>-6.651501200000002</v>
       </c>
       <c r="O52">
-        <v>-1.61489</v>
+        <v>-1.662875300000001</v>
       </c>
       <c r="P52">
-        <v>-4.844670000000001</v>
+        <v>-4.988625900000002</v>
       </c>
       <c r="Q52">
-        <v>-4.81967</v>
+        <v>-4.963625900000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.145315856434768</v>
+        <v>0.1473467922803755</v>
       </c>
       <c r="T52">
-        <v>0.9623943899413192</v>
+        <v>0.9820350917768562</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.08173075921167523</v>
+        <v>0.08012819530556395</v>
       </c>
       <c r="W52">
-        <v>0.216527886977887</v>
+        <v>0.216905771546948</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3269230368467009</v>
+        <v>0.3205127812222557</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1828218717063275</v>
+        <v>0.1847218717063275</v>
       </c>
       <c r="C53">
-        <v>-5.470290116148817</v>
+        <v>-6.729245600984122</v>
       </c>
       <c r="D53">
-        <v>32.53370988385119</v>
+        <v>32.08875439901588</v>
       </c>
       <c r="E53">
-        <v>14.514</v>
+        <v>15.328</v>
       </c>
       <c r="F53">
-        <v>41.514</v>
+        <v>42.328</v>
       </c>
       <c r="G53">
         <v>3.51</v>
@@ -5633,37 +5633,37 @@
         <v>3.1375</v>
       </c>
       <c r="M53">
-        <v>9.789001200000001</v>
+        <v>9.980942400000002</v>
       </c>
       <c r="N53">
-        <v>-6.651501200000002</v>
+        <v>-6.843442400000002</v>
       </c>
       <c r="O53">
-        <v>-1.662875300000001</v>
+        <v>-1.710860600000001</v>
       </c>
       <c r="P53">
-        <v>-4.988625900000002</v>
+        <v>-5.132581800000002</v>
       </c>
       <c r="Q53">
-        <v>-4.963625900000001</v>
+        <v>-5.107581800000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1473467922803755</v>
+        <v>0.1494623504528834</v>
       </c>
       <c r="T53">
-        <v>0.9820350917768562</v>
+        <v>1.002494156188874</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.08012819530556395</v>
+        <v>0.07858726847276463</v>
       </c>
       <c r="W53">
-        <v>0.216905771546948</v>
+        <v>0.2172691220941221</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3205127812222557</v>
+        <v>0.3143490738910585</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1847218717063275</v>
+        <v>0.1866218717063275</v>
       </c>
       <c r="C54">
-        <v>-6.729245600984122</v>
+        <v>-7.97619420917529</v>
       </c>
       <c r="D54">
-        <v>32.08875439901588</v>
+        <v>31.65580579082471</v>
       </c>
       <c r="E54">
-        <v>15.328</v>
+        <v>16.142</v>
       </c>
       <c r="F54">
-        <v>42.328</v>
+        <v>43.142</v>
       </c>
       <c r="G54">
         <v>3.51</v>
@@ -5715,37 +5715,37 @@
         <v>3.1375</v>
       </c>
       <c r="M54">
-        <v>9.980942400000002</v>
+        <v>10.1728836</v>
       </c>
       <c r="N54">
-        <v>-6.843442400000002</v>
+        <v>-7.035383600000001</v>
       </c>
       <c r="O54">
-        <v>-1.710860600000001</v>
+        <v>-1.7588459</v>
       </c>
       <c r="P54">
-        <v>-5.132581800000002</v>
+        <v>-5.2765377</v>
       </c>
       <c r="Q54">
-        <v>-5.107581800000002</v>
+        <v>-5.2515377</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1494623504528834</v>
+        <v>0.1516679323774128</v>
       </c>
       <c r="T54">
-        <v>1.002494156188874</v>
+        <v>1.02382381908651</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07858726847276463</v>
+        <v>0.07710448982233513</v>
       </c>
       <c r="W54">
-        <v>0.2172691220941221</v>
+        <v>0.2176187612998934</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3143490738910585</v>
+        <v>0.3084179592893405</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1866218717063275</v>
+        <v>0.1885218717063275</v>
       </c>
       <c r="C55">
-        <v>-7.97619420917529</v>
+        <v>-9.211615469164975</v>
       </c>
       <c r="D55">
-        <v>31.65580579082471</v>
+        <v>31.23438453083503</v>
       </c>
       <c r="E55">
-        <v>16.142</v>
+        <v>16.956</v>
       </c>
       <c r="F55">
-        <v>43.142</v>
+        <v>43.956</v>
       </c>
       <c r="G55">
         <v>3.51</v>
@@ -5797,37 +5797,37 @@
         <v>3.1375</v>
       </c>
       <c r="M55">
-        <v>10.1728836</v>
+        <v>10.3648248</v>
       </c>
       <c r="N55">
-        <v>-7.035383600000001</v>
+        <v>-7.227324800000002</v>
       </c>
       <c r="O55">
-        <v>-1.7588459</v>
+        <v>-1.8068312</v>
       </c>
       <c r="P55">
-        <v>-5.2765377</v>
+        <v>-5.420493600000001</v>
       </c>
       <c r="Q55">
-        <v>-5.2515377</v>
+        <v>-5.395493600000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1516679323774128</v>
+        <v>0.1539694091682261</v>
       </c>
       <c r="T55">
-        <v>1.02382381908651</v>
+        <v>1.046080858631869</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.07710448982233513</v>
+        <v>0.07567662889969928</v>
       </c>
       <c r="W55">
-        <v>0.2176187612998934</v>
+        <v>0.2179554509054509</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3084179592893405</v>
+        <v>0.3027065155987971</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1885218717063275</v>
+        <v>0.1904218717063275</v>
       </c>
       <c r="C56">
-        <v>-9.211615469164975</v>
+        <v>-10.43596370977616</v>
       </c>
       <c r="D56">
-        <v>31.23438453083503</v>
+        <v>30.82403629022385</v>
       </c>
       <c r="E56">
-        <v>16.956</v>
+        <v>17.77000000000001</v>
       </c>
       <c r="F56">
-        <v>43.956</v>
+        <v>44.77000000000001</v>
       </c>
       <c r="G56">
         <v>3.51</v>
@@ -5879,37 +5879,37 @@
         <v>3.1375</v>
       </c>
       <c r="M56">
-        <v>10.3648248</v>
+        <v>10.556766</v>
       </c>
       <c r="N56">
-        <v>-7.227324800000002</v>
+        <v>-7.419266000000004</v>
       </c>
       <c r="O56">
-        <v>-1.8068312</v>
+        <v>-1.854816500000001</v>
       </c>
       <c r="P56">
-        <v>-5.420493600000001</v>
+        <v>-5.564449500000003</v>
       </c>
       <c r="Q56">
-        <v>-5.395493600000001</v>
+        <v>-5.539449500000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1539694091682261</v>
+        <v>0.1563731738164089</v>
       </c>
       <c r="T56">
-        <v>1.046080858631869</v>
+        <v>1.069327099934799</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.07567662889969928</v>
+        <v>0.074300690192432</v>
       </c>
       <c r="W56">
-        <v>0.2179554509054509</v>
+        <v>0.2182798972526245</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3027065155987971</v>
+        <v>0.297202760769728</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1904218717063275</v>
+        <v>0.1923218717063275</v>
       </c>
       <c r="C57">
-        <v>-10.43596370977616</v>
+        <v>-11.64966969407322</v>
       </c>
       <c r="D57">
-        <v>30.82403629022385</v>
+        <v>30.42433030592679</v>
       </c>
       <c r="E57">
-        <v>17.77000000000001</v>
+        <v>18.58400000000001</v>
       </c>
       <c r="F57">
-        <v>44.77000000000001</v>
+        <v>45.58400000000001</v>
       </c>
       <c r="G57">
         <v>3.51</v>
@@ -5961,37 +5961,37 @@
         <v>3.1375</v>
       </c>
       <c r="M57">
-        <v>10.556766</v>
+        <v>10.7487072</v>
       </c>
       <c r="N57">
-        <v>-7.419266000000004</v>
+        <v>-7.611207200000004</v>
       </c>
       <c r="O57">
-        <v>-1.854816500000001</v>
+        <v>-1.902801800000001</v>
       </c>
       <c r="P57">
-        <v>-5.564449500000003</v>
+        <v>-5.708405400000004</v>
       </c>
       <c r="Q57">
-        <v>-5.539449500000003</v>
+        <v>-5.683405400000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1563731738164089</v>
+        <v>0.1588862004940546</v>
       </c>
       <c r="T57">
-        <v>1.069327099934799</v>
+        <v>1.093629988569681</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.074300690192432</v>
+        <v>0.07297389215328144</v>
       </c>
       <c r="W57">
-        <v>0.2182798972526245</v>
+        <v>0.2185927562302563</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.297202760769728</v>
+        <v>0.2918955686131257</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1923218717063275</v>
+        <v>0.1942218717063275</v>
       </c>
       <c r="C58">
-        <v>-11.64966969407322</v>
+        <v>-12.85314212772935</v>
       </c>
       <c r="D58">
-        <v>30.42433030592679</v>
+        <v>30.03485787227066</v>
       </c>
       <c r="E58">
-        <v>18.58400000000001</v>
+        <v>19.39800000000001</v>
       </c>
       <c r="F58">
-        <v>45.58400000000001</v>
+        <v>46.39800000000001</v>
       </c>
       <c r="G58">
         <v>3.51</v>
@@ -6043,37 +6043,37 @@
         <v>3.1375</v>
       </c>
       <c r="M58">
-        <v>10.7487072</v>
+        <v>10.9406484</v>
       </c>
       <c r="N58">
-        <v>-7.611207200000004</v>
+        <v>-7.803148400000003</v>
       </c>
       <c r="O58">
-        <v>-1.902801800000001</v>
+        <v>-1.950787100000001</v>
       </c>
       <c r="P58">
-        <v>-5.708405400000004</v>
+        <v>-5.852361300000002</v>
       </c>
       <c r="Q58">
-        <v>-5.683405400000003</v>
+        <v>-5.827361300000002</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1588862004940546</v>
+        <v>0.1615161121334512</v>
       </c>
       <c r="T58">
-        <v>1.093629988569681</v>
+        <v>1.119063244117813</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.07297389215328144</v>
+        <v>0.07169364843129405</v>
       </c>
       <c r="W58">
-        <v>0.2185927562302563</v>
+        <v>0.2188946376999009</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2918955686131257</v>
+        <v>0.2867745937251761</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1942218717063275</v>
+        <v>0.1961218717063275</v>
       </c>
       <c r="C59">
-        <v>-12.85314212772935</v>
+        <v>-14.04676905300341</v>
       </c>
       <c r="D59">
-        <v>30.03485787227066</v>
+        <v>29.6552309469966</v>
       </c>
       <c r="E59">
-        <v>19.39800000000001</v>
+        <v>20.21200000000001</v>
       </c>
       <c r="F59">
-        <v>46.39800000000001</v>
+        <v>47.21200000000001</v>
       </c>
       <c r="G59">
         <v>3.51</v>
@@ -6125,37 +6125,37 @@
         <v>3.1375</v>
       </c>
       <c r="M59">
-        <v>10.9406484</v>
+        <v>11.1325896</v>
       </c>
       <c r="N59">
-        <v>-7.803148400000003</v>
+        <v>-7.995089600000004</v>
       </c>
       <c r="O59">
-        <v>-1.950787100000001</v>
+        <v>-1.998772400000001</v>
       </c>
       <c r="P59">
-        <v>-5.852361300000002</v>
+        <v>-5.996317200000003</v>
       </c>
       <c r="Q59">
-        <v>-5.827361300000002</v>
+        <v>-5.971317200000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1615161121334512</v>
+        <v>0.1642712576604382</v>
       </c>
       <c r="T59">
-        <v>1.119063244117813</v>
+        <v>1.145707607072999</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.07169364843129405</v>
+        <v>0.07045755104454759</v>
       </c>
       <c r="W59">
-        <v>0.2188946376999009</v>
+        <v>0.2191861094636957</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2867745937251761</v>
+        <v>0.2818302041781904</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1961218717063275</v>
+        <v>0.1980218717063275</v>
       </c>
       <c r="C60">
-        <v>-14.04676905300339</v>
+        <v>-15.23091913832094</v>
       </c>
       <c r="D60">
-        <v>29.65523094699661</v>
+        <v>29.28508086167906</v>
       </c>
       <c r="E60">
-        <v>20.212</v>
+        <v>21.026</v>
       </c>
       <c r="F60">
-        <v>47.212</v>
+        <v>48.026</v>
       </c>
       <c r="G60">
         <v>3.51</v>
@@ -6207,37 +6207,37 @@
         <v>3.1375</v>
       </c>
       <c r="M60">
-        <v>11.1325896</v>
+        <v>11.3245308</v>
       </c>
       <c r="N60">
-        <v>-7.995089600000002</v>
+        <v>-8.187030800000002</v>
       </c>
       <c r="O60">
-        <v>-1.9987724</v>
+        <v>-2.046757700000001</v>
       </c>
       <c r="P60">
-        <v>-5.996317200000002</v>
+        <v>-6.140273100000002</v>
       </c>
       <c r="Q60">
-        <v>-5.971317200000001</v>
+        <v>-6.115273100000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1642712576604381</v>
+        <v>0.1671608005302049</v>
       </c>
       <c r="T60">
-        <v>1.145707607072999</v>
+        <v>1.173651695050389</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.07045755104454761</v>
+        <v>0.06926335526413155</v>
       </c>
       <c r="W60">
-        <v>0.2191861094636957</v>
+        <v>0.2194677008287178</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2818302041781904</v>
+        <v>0.2770534210565262</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1980218717063275</v>
+        <v>0.1999218717063275</v>
       </c>
       <c r="C61">
-        <v>-15.23091913832094</v>
+        <v>-16.40594287246824</v>
       </c>
       <c r="D61">
-        <v>29.28508086167906</v>
+        <v>28.92405712753177</v>
       </c>
       <c r="E61">
-        <v>21.026</v>
+        <v>21.84</v>
       </c>
       <c r="F61">
-        <v>48.026</v>
+        <v>48.84</v>
       </c>
       <c r="G61">
         <v>3.51</v>
@@ -6289,37 +6289,37 @@
         <v>3.1375</v>
       </c>
       <c r="M61">
-        <v>11.3245308</v>
+        <v>11.516472</v>
       </c>
       <c r="N61">
-        <v>-8.187030800000002</v>
+        <v>-8.378972000000003</v>
       </c>
       <c r="O61">
-        <v>-2.046757700000001</v>
+        <v>-2.094743000000001</v>
       </c>
       <c r="P61">
-        <v>-6.140273100000002</v>
+        <v>-6.284229000000002</v>
       </c>
       <c r="Q61">
-        <v>-6.115273100000001</v>
+        <v>-6.259229000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1671608005302049</v>
+        <v>0.17019482054346</v>
       </c>
       <c r="T61">
-        <v>1.173651695050389</v>
+        <v>1.202992987426649</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06926335526413155</v>
+        <v>0.06810896600972935</v>
       </c>
       <c r="W61">
-        <v>0.2194677008287178</v>
+        <v>0.2197399058149058</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2770534210565262</v>
+        <v>0.2724358640389174</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1999218717063275</v>
+        <v>0.2018218717063275</v>
       </c>
       <c r="C62">
-        <v>-16.40594287246824</v>
+        <v>-17.57217367153051</v>
       </c>
       <c r="D62">
-        <v>28.92405712753177</v>
+        <v>28.57182632846949</v>
       </c>
       <c r="E62">
-        <v>21.84</v>
+        <v>22.654</v>
       </c>
       <c r="F62">
-        <v>48.84</v>
+        <v>49.654</v>
       </c>
       <c r="G62">
         <v>3.51</v>
@@ -6371,37 +6371,37 @@
         <v>3.1375</v>
       </c>
       <c r="M62">
-        <v>11.516472</v>
+        <v>11.7084132</v>
       </c>
       <c r="N62">
-        <v>-8.378972000000003</v>
+        <v>-8.570913200000001</v>
       </c>
       <c r="O62">
-        <v>-2.094743000000001</v>
+        <v>-2.1427283</v>
       </c>
       <c r="P62">
-        <v>-6.284229000000002</v>
+        <v>-6.428184900000002</v>
       </c>
       <c r="Q62">
-        <v>-6.259229000000001</v>
+        <v>-6.403184900000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.17019482054346</v>
+        <v>0.1733844313266257</v>
       </c>
       <c r="T62">
-        <v>1.202992987426649</v>
+        <v>1.23383896146323</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.06810896600972935</v>
+        <v>0.06699242558334036</v>
       </c>
       <c r="W62">
-        <v>0.2197399058149058</v>
+        <v>0.2200031860474483</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2724358640389174</v>
+        <v>0.2679697023333614</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2018218717063275</v>
+        <v>0.2037218717063275</v>
       </c>
       <c r="C63">
-        <v>-17.57217367153051</v>
+        <v>-18.7299289059229</v>
       </c>
       <c r="D63">
-        <v>28.57182632846949</v>
+        <v>28.22807109407711</v>
       </c>
       <c r="E63">
-        <v>22.654</v>
+        <v>23.468</v>
       </c>
       <c r="F63">
-        <v>49.654</v>
+        <v>50.468</v>
       </c>
       <c r="G63">
         <v>3.51</v>
@@ -6453,37 +6453,37 @@
         <v>3.1375</v>
       </c>
       <c r="M63">
-        <v>11.7084132</v>
+        <v>11.9003544</v>
       </c>
       <c r="N63">
-        <v>-8.570913200000001</v>
+        <v>-8.762854400000002</v>
       </c>
       <c r="O63">
-        <v>-2.1427283</v>
+        <v>-2.1907136</v>
       </c>
       <c r="P63">
-        <v>-6.428184900000002</v>
+        <v>-6.572140800000001</v>
       </c>
       <c r="Q63">
-        <v>-6.403184900000001</v>
+        <v>-6.547140800000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1733844313266257</v>
+        <v>0.1767419163615369</v>
       </c>
       <c r="T63">
-        <v>1.23383896146323</v>
+        <v>1.266308407817525</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.06699242558334036</v>
+        <v>0.06591190259006066</v>
       </c>
       <c r="W63">
-        <v>0.2200031860474483</v>
+        <v>0.2202579733692637</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2679697023333614</v>
+        <v>0.2636476103602426</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2037218717063275</v>
+        <v>0.2056218717063275</v>
       </c>
       <c r="C64">
-        <v>-18.7299289059229</v>
+        <v>-19.87951085416399</v>
       </c>
       <c r="D64">
-        <v>28.22807109407711</v>
+        <v>27.89248914583602</v>
       </c>
       <c r="E64">
-        <v>23.468</v>
+        <v>24.282</v>
       </c>
       <c r="F64">
-        <v>50.468</v>
+        <v>51.282</v>
       </c>
       <c r="G64">
         <v>3.51</v>
@@ -6535,37 +6535,37 @@
         <v>3.1375</v>
       </c>
       <c r="M64">
-        <v>11.9003544</v>
+        <v>12.0922956</v>
       </c>
       <c r="N64">
-        <v>-8.762854400000002</v>
+        <v>-8.954795600000002</v>
       </c>
       <c r="O64">
-        <v>-2.1907136</v>
+        <v>-2.238698900000001</v>
       </c>
       <c r="P64">
-        <v>-6.572140800000001</v>
+        <v>-6.716096700000001</v>
       </c>
       <c r="Q64">
-        <v>-6.547140800000001</v>
+        <v>-6.691096700000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1767419163615369</v>
+        <v>0.1802808870740108</v>
       </c>
       <c r="T64">
-        <v>1.266308407817525</v>
+        <v>1.300532959380161</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.06591190259006066</v>
+        <v>0.06486568191402796</v>
       </c>
       <c r="W64">
-        <v>0.2202579733692637</v>
+        <v>0.2205046722046722</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2636476103602426</v>
+        <v>0.2594627276561118</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2056218717063275</v>
+        <v>0.2075218717063275</v>
       </c>
       <c r="C65">
-        <v>-19.87951085416399</v>
+        <v>-21.02120758941649</v>
       </c>
       <c r="D65">
-        <v>27.89248914583602</v>
+        <v>27.56479241058351</v>
       </c>
       <c r="E65">
-        <v>24.282</v>
+        <v>25.096</v>
       </c>
       <c r="F65">
-        <v>51.282</v>
+        <v>52.096</v>
       </c>
       <c r="G65">
         <v>3.51</v>
@@ -6617,37 +6617,37 @@
         <v>3.1375</v>
       </c>
       <c r="M65">
-        <v>12.0922956</v>
+        <v>12.2842368</v>
       </c>
       <c r="N65">
-        <v>-8.954795600000002</v>
+        <v>-9.146736800000003</v>
       </c>
       <c r="O65">
-        <v>-2.238698900000001</v>
+        <v>-2.286684200000001</v>
       </c>
       <c r="P65">
-        <v>-6.716096700000001</v>
+        <v>-6.860052600000002</v>
       </c>
       <c r="Q65">
-        <v>-6.691096700000001</v>
+        <v>-6.835052600000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1802808870740108</v>
+        <v>0.1840164672705111</v>
       </c>
       <c r="T65">
-        <v>1.300532959380161</v>
+        <v>1.336658874918499</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.06486568191402796</v>
+        <v>0.06385215563412126</v>
       </c>
       <c r="W65">
-        <v>0.2205046722046722</v>
+        <v>0.2207436617014742</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2594627276561118</v>
+        <v>0.255408622536485</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2075218717063275</v>
+        <v>0.2094218717063275</v>
       </c>
       <c r="C66">
-        <v>-21.02120758941649</v>
+        <v>-22.15529380426013</v>
       </c>
       <c r="D66">
-        <v>27.56479241058351</v>
+        <v>27.24470619573988</v>
       </c>
       <c r="E66">
-        <v>25.096</v>
+        <v>25.91</v>
       </c>
       <c r="F66">
-        <v>52.096</v>
+        <v>52.91</v>
       </c>
       <c r="G66">
         <v>3.51</v>
@@ -6699,37 +6699,37 @@
         <v>3.1375</v>
       </c>
       <c r="M66">
-        <v>12.2842368</v>
+        <v>12.476178</v>
       </c>
       <c r="N66">
-        <v>-9.146736800000003</v>
+        <v>-9.338678000000002</v>
       </c>
       <c r="O66">
-        <v>-2.286684200000001</v>
+        <v>-2.3346695</v>
       </c>
       <c r="P66">
-        <v>-6.860052600000002</v>
+        <v>-7.004008500000001</v>
       </c>
       <c r="Q66">
-        <v>-6.835052600000002</v>
+        <v>-6.979008500000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1840164672705111</v>
+        <v>0.1879655091925258</v>
       </c>
       <c r="T66">
-        <v>1.336658874918499</v>
+        <v>1.374849128487599</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.06385215563412126</v>
+        <v>0.06286981477821171</v>
       </c>
       <c r="W66">
-        <v>0.2207436617014742</v>
+        <v>0.2209752976752977</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.255408622536485</v>
+        <v>0.2514792591128469</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2094218717063275</v>
+        <v>0.2113218717063275</v>
       </c>
       <c r="C67">
-        <v>-22.15529380426013</v>
+        <v>-23.2820315786598</v>
       </c>
       <c r="D67">
-        <v>27.24470619573988</v>
+        <v>26.9319684213402</v>
       </c>
       <c r="E67">
-        <v>25.91</v>
+        <v>26.724</v>
       </c>
       <c r="F67">
-        <v>52.91</v>
+        <v>53.724</v>
       </c>
       <c r="G67">
         <v>3.51</v>
@@ -6781,37 +6781,37 @@
         <v>3.1375</v>
       </c>
       <c r="M67">
-        <v>12.476178</v>
+        <v>12.6681192</v>
       </c>
       <c r="N67">
-        <v>-9.338678000000002</v>
+        <v>-9.530619200000002</v>
       </c>
       <c r="O67">
-        <v>-2.3346695</v>
+        <v>-2.382654800000001</v>
       </c>
       <c r="P67">
-        <v>-7.004008500000001</v>
+        <v>-7.147964400000001</v>
       </c>
       <c r="Q67">
-        <v>-6.979008500000001</v>
+        <v>-7.122964400000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1879655091925258</v>
+        <v>0.1921468476981883</v>
       </c>
       <c r="T67">
-        <v>1.374849128487599</v>
+        <v>1.415285867560764</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.06286981477821171</v>
+        <v>0.06191724182702669</v>
       </c>
       <c r="W67">
-        <v>0.2209752976752977</v>
+        <v>0.2211999143771871</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2514792591128469</v>
+        <v>0.2476689673081067</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2113218717063275</v>
+        <v>0.2132218717063275</v>
       </c>
       <c r="C68">
-        <v>-23.2820315786598</v>
+        <v>-24.40167109564181</v>
       </c>
       <c r="D68">
-        <v>26.9319684213402</v>
+        <v>26.62632890435819</v>
       </c>
       <c r="E68">
-        <v>26.724</v>
+        <v>27.538</v>
       </c>
       <c r="F68">
-        <v>53.724</v>
+        <v>54.538</v>
       </c>
       <c r="G68">
         <v>3.51</v>
@@ -6863,37 +6863,37 @@
         <v>3.1375</v>
       </c>
       <c r="M68">
-        <v>12.6681192</v>
+        <v>12.8600604</v>
       </c>
       <c r="N68">
-        <v>-9.530619200000002</v>
+        <v>-9.722560400000003</v>
       </c>
       <c r="O68">
-        <v>-2.382654800000001</v>
+        <v>-2.430640100000001</v>
       </c>
       <c r="P68">
-        <v>-7.147964400000001</v>
+        <v>-7.291920300000002</v>
       </c>
       <c r="Q68">
-        <v>-7.122964400000001</v>
+        <v>-7.266920300000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1921468476981883</v>
+        <v>0.1965816006587394</v>
       </c>
       <c r="T68">
-        <v>1.415285867560764</v>
+        <v>1.458173318092908</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.06191724182702669</v>
+        <v>0.06099310388930987</v>
       </c>
       <c r="W68">
-        <v>0.2211999143771871</v>
+        <v>0.2214178261029007</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2476689673081067</v>
+        <v>0.2439724155572395</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2132218717063275</v>
+        <v>0.2151218717063275</v>
       </c>
       <c r="C69">
-        <v>-24.40167109564181</v>
+        <v>-25.51445130878536</v>
       </c>
       <c r="D69">
-        <v>26.62632890435819</v>
+        <v>26.32754869121465</v>
       </c>
       <c r="E69">
-        <v>27.538</v>
+        <v>28.35200000000001</v>
       </c>
       <c r="F69">
-        <v>54.538</v>
+        <v>55.35200000000001</v>
       </c>
       <c r="G69">
         <v>3.51</v>
@@ -6945,37 +6945,37 @@
         <v>3.1375</v>
       </c>
       <c r="M69">
-        <v>12.8600604</v>
+        <v>13.0520016</v>
       </c>
       <c r="N69">
-        <v>-9.722560400000003</v>
+        <v>-9.914501600000003</v>
       </c>
       <c r="O69">
-        <v>-2.430640100000001</v>
+        <v>-2.478625400000001</v>
       </c>
       <c r="P69">
-        <v>-7.291920300000002</v>
+        <v>-7.435876200000003</v>
       </c>
       <c r="Q69">
-        <v>-7.266920300000002</v>
+        <v>-7.410876200000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1965816006587394</v>
+        <v>0.2012935256793251</v>
       </c>
       <c r="T69">
-        <v>1.458173318092908</v>
+        <v>1.503741234283311</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06099310388930987</v>
+        <v>0.06009614647917295</v>
       </c>
       <c r="W69">
-        <v>0.2214178261029007</v>
+        <v>0.221629328660211</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2439724155572395</v>
+        <v>0.2403845859166918</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2151218717063275</v>
+        <v>0.2170218717063275</v>
       </c>
       <c r="C70">
-        <v>-25.51445130878536</v>
+        <v>-26.62060056527233</v>
       </c>
       <c r="D70">
-        <v>26.32754869121465</v>
+        <v>26.03539943472769</v>
       </c>
       <c r="E70">
-        <v>28.35200000000001</v>
+        <v>29.16600000000001</v>
       </c>
       <c r="F70">
-        <v>55.35200000000001</v>
+        <v>56.16600000000001</v>
       </c>
       <c r="G70">
         <v>3.51</v>
@@ -7027,37 +7027,37 @@
         <v>3.1375</v>
       </c>
       <c r="M70">
-        <v>13.0520016</v>
+        <v>13.2439428</v>
       </c>
       <c r="N70">
-        <v>-9.914501600000003</v>
+        <v>-10.1064428</v>
       </c>
       <c r="O70">
-        <v>-2.478625400000001</v>
+        <v>-2.526610700000001</v>
       </c>
       <c r="P70">
-        <v>-7.435876200000003</v>
+        <v>-7.579832100000003</v>
       </c>
       <c r="Q70">
-        <v>-7.410876200000002</v>
+        <v>-7.554832100000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2012935256793251</v>
+        <v>0.2063094458625291</v>
       </c>
       <c r="T70">
-        <v>1.503741234283311</v>
+        <v>1.552249016034386</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.06009614647917295</v>
+        <v>0.05922518783454726</v>
       </c>
       <c r="W70">
-        <v>0.221629328660211</v>
+        <v>0.2218347007086138</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2403845859166918</v>
+        <v>0.236900751338189</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2170218717063275</v>
+        <v>0.2189218717063275</v>
       </c>
       <c r="C71">
-        <v>-26.62060056527233</v>
+        <v>-27.72033718790944</v>
       </c>
       <c r="D71">
-        <v>26.03539943472769</v>
+        <v>25.74966281209057</v>
       </c>
       <c r="E71">
-        <v>29.16600000000001</v>
+        <v>29.98000000000001</v>
       </c>
       <c r="F71">
-        <v>56.16600000000001</v>
+        <v>56.98000000000001</v>
       </c>
       <c r="G71">
         <v>3.51</v>
@@ -7109,37 +7109,37 @@
         <v>3.1375</v>
       </c>
       <c r="M71">
-        <v>13.2439428</v>
+        <v>13.435884</v>
       </c>
       <c r="N71">
-        <v>-10.1064428</v>
+        <v>-10.298384</v>
       </c>
       <c r="O71">
-        <v>-2.526610700000001</v>
+        <v>-2.574596000000001</v>
       </c>
       <c r="P71">
-        <v>-7.579832100000003</v>
+        <v>-7.723788000000003</v>
       </c>
       <c r="Q71">
-        <v>-7.554832100000002</v>
+        <v>-7.698788000000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2063094458625291</v>
+        <v>0.2116597607246134</v>
       </c>
       <c r="T71">
-        <v>1.552249016034386</v>
+        <v>1.603990649902199</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05922518783454726</v>
+        <v>0.05837911372262515</v>
       </c>
       <c r="W71">
-        <v>0.2218347007086138</v>
+        <v>0.222034204984205</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.236900751338189</v>
+        <v>0.2335164548905005</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2189218717063275</v>
+        <v>0.2208218717063276</v>
       </c>
       <c r="C72">
-        <v>-27.72033718790944</v>
+        <v>-28.81387001924073</v>
       </c>
       <c r="D72">
-        <v>25.74966281209057</v>
+        <v>25.47012998075928</v>
       </c>
       <c r="E72">
-        <v>29.98000000000001</v>
+        <v>30.79400000000001</v>
       </c>
       <c r="F72">
-        <v>56.98000000000001</v>
+        <v>57.79400000000001</v>
       </c>
       <c r="G72">
         <v>3.51</v>
@@ -7191,37 +7191,37 @@
         <v>3.1375</v>
       </c>
       <c r="M72">
-        <v>13.435884</v>
+        <v>13.6278252</v>
       </c>
       <c r="N72">
-        <v>-10.298384</v>
+        <v>-10.4903252</v>
       </c>
       <c r="O72">
-        <v>-2.574596000000001</v>
+        <v>-2.622581300000001</v>
       </c>
       <c r="P72">
-        <v>-7.723788000000003</v>
+        <v>-7.867743900000003</v>
       </c>
       <c r="Q72">
-        <v>-7.698788000000002</v>
+        <v>-7.842743900000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2116597607246134</v>
+        <v>0.2173790628185656</v>
       </c>
       <c r="T72">
-        <v>1.603990649902199</v>
+        <v>1.65930067231262</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05837911372262515</v>
+        <v>0.05755687268427832</v>
       </c>
       <c r="W72">
-        <v>0.222034204984205</v>
+        <v>0.2222280894210472</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2335164548905005</v>
+        <v>0.2302274907371132</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2208218717063275</v>
+        <v>0.2227218717063275</v>
       </c>
       <c r="C73">
-        <v>-28.81387001924072</v>
+        <v>-29.9013989305998</v>
       </c>
       <c r="D73">
-        <v>25.47012998075929</v>
+        <v>25.19660106940021</v>
       </c>
       <c r="E73">
-        <v>30.794</v>
+        <v>31.608</v>
       </c>
       <c r="F73">
-        <v>57.794</v>
+        <v>58.608</v>
       </c>
       <c r="G73">
         <v>3.51</v>
@@ -7273,37 +7273,37 @@
         <v>3.1375</v>
       </c>
       <c r="M73">
-        <v>13.6278252</v>
+        <v>13.8197664</v>
       </c>
       <c r="N73">
-        <v>-10.4903252</v>
+        <v>-10.6822664</v>
       </c>
       <c r="O73">
-        <v>-2.622581300000001</v>
+        <v>-2.6705666</v>
       </c>
       <c r="P73">
-        <v>-7.867743900000002</v>
+        <v>-8.011699800000001</v>
       </c>
       <c r="Q73">
-        <v>-7.842743900000002</v>
+        <v>-7.9866998</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2173790628185655</v>
+        <v>0.2235068864906572</v>
       </c>
       <c r="T73">
-        <v>1.659300672312619</v>
+        <v>1.718561410609498</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05755687268427832</v>
+        <v>0.05675747167477447</v>
       </c>
       <c r="W73">
-        <v>0.2222280894210472</v>
+        <v>0.2224165881790882</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2302274907371132</v>
+        <v>0.2270298866990978</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2227218717063275</v>
+        <v>0.2246218717063275</v>
       </c>
       <c r="C74">
-        <v>-29.9013989305998</v>
+        <v>-30.98311529870985</v>
       </c>
       <c r="D74">
-        <v>25.19660106940021</v>
+        <v>24.92888470129015</v>
       </c>
       <c r="E74">
-        <v>31.608</v>
+        <v>32.422</v>
       </c>
       <c r="F74">
-        <v>58.608</v>
+        <v>59.422</v>
       </c>
       <c r="G74">
         <v>3.51</v>
@@ -7355,37 +7355,37 @@
         <v>3.1375</v>
       </c>
       <c r="M74">
-        <v>13.8197664</v>
+        <v>14.0117076</v>
       </c>
       <c r="N74">
-        <v>-10.6822664</v>
+        <v>-10.8742076</v>
       </c>
       <c r="O74">
-        <v>-2.6705666</v>
+        <v>-2.7185519</v>
       </c>
       <c r="P74">
-        <v>-8.011699800000001</v>
+        <v>-8.155655700000001</v>
       </c>
       <c r="Q74">
-        <v>-7.9866998</v>
+        <v>-8.1306557</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2235068864906572</v>
+        <v>0.2300886230273482</v>
       </c>
       <c r="T74">
-        <v>1.718561410609498</v>
+        <v>1.782211833224665</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05675747167477447</v>
+        <v>0.05597997206279125</v>
       </c>
       <c r="W74">
-        <v>0.2224165881790882</v>
+        <v>0.2225999225875938</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2270298866990978</v>
+        <v>0.2239198882511649</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2246218717063275</v>
+        <v>0.2265218717063275</v>
       </c>
       <c r="C75">
-        <v>-30.98311529870985</v>
+        <v>-32.05920245221953</v>
       </c>
       <c r="D75">
-        <v>24.92888470129015</v>
+        <v>24.66679754778048</v>
       </c>
       <c r="E75">
-        <v>32.422</v>
+        <v>33.236</v>
       </c>
       <c r="F75">
-        <v>59.422</v>
+        <v>60.236</v>
       </c>
       <c r="G75">
         <v>3.51</v>
@@ -7437,37 +7437,37 @@
         <v>3.1375</v>
       </c>
       <c r="M75">
-        <v>14.0117076</v>
+        <v>14.2036488</v>
       </c>
       <c r="N75">
-        <v>-10.8742076</v>
+        <v>-11.0661488</v>
       </c>
       <c r="O75">
-        <v>-2.7185519</v>
+        <v>-2.766537200000001</v>
       </c>
       <c r="P75">
-        <v>-8.155655700000001</v>
+        <v>-8.299611600000002</v>
       </c>
       <c r="Q75">
-        <v>-8.1306557</v>
+        <v>-8.274611600000002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2300886230273482</v>
+        <v>0.2371766469899385</v>
       </c>
       <c r="T75">
-        <v>1.782211833224665</v>
+        <v>1.850758442194844</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05597997206279125</v>
+        <v>0.05522348595383461</v>
       </c>
       <c r="W75">
-        <v>0.2225999225875938</v>
+        <v>0.2227783020120858</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2239198882511649</v>
+        <v>0.2208939438153384</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2265218717063275</v>
+        <v>0.2284218717063275</v>
       </c>
       <c r="C76">
-        <v>-32.05920245221953</v>
+        <v>-33.12983609036419</v>
       </c>
       <c r="D76">
-        <v>24.66679754778048</v>
+        <v>24.41016390963581</v>
       </c>
       <c r="E76">
-        <v>33.236</v>
+        <v>34.05</v>
       </c>
       <c r="F76">
-        <v>60.236</v>
+        <v>61.05</v>
       </c>
       <c r="G76">
         <v>3.51</v>
@@ -7519,37 +7519,37 @@
         <v>3.1375</v>
       </c>
       <c r="M76">
-        <v>14.2036488</v>
+        <v>14.39559</v>
       </c>
       <c r="N76">
-        <v>-11.0661488</v>
+        <v>-11.25809</v>
       </c>
       <c r="O76">
-        <v>-2.766537200000001</v>
+        <v>-2.814522500000001</v>
       </c>
       <c r="P76">
-        <v>-8.299611600000002</v>
+        <v>-8.443567500000002</v>
       </c>
       <c r="Q76">
-        <v>-8.274611600000002</v>
+        <v>-8.418567500000002</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2371766469899385</v>
+        <v>0.2448317128695361</v>
       </c>
       <c r="T76">
-        <v>1.850758442194844</v>
+        <v>1.924788779882638</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.05522348595383461</v>
+        <v>0.05448717280778348</v>
       </c>
       <c r="W76">
-        <v>0.2227783020120858</v>
+        <v>0.2229519246519247</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2208939438153384</v>
+        <v>0.2179486912311339</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2284218717063275</v>
+        <v>0.2303218717063275</v>
       </c>
       <c r="C77">
-        <v>-33.12983609036419</v>
+        <v>-34.19518467576183</v>
       </c>
       <c r="D77">
-        <v>24.41016390963581</v>
+        <v>24.15881532423818</v>
       </c>
       <c r="E77">
-        <v>34.05</v>
+        <v>34.864</v>
       </c>
       <c r="F77">
-        <v>61.05</v>
+        <v>61.864</v>
       </c>
       <c r="G77">
         <v>3.51</v>
@@ -7601,37 +7601,37 @@
         <v>3.1375</v>
       </c>
       <c r="M77">
-        <v>14.39559</v>
+        <v>14.5875312</v>
       </c>
       <c r="N77">
-        <v>-11.25809</v>
+        <v>-11.4500312</v>
       </c>
       <c r="O77">
-        <v>-2.814522500000001</v>
+        <v>-2.8625078</v>
       </c>
       <c r="P77">
-        <v>-8.443567500000002</v>
+        <v>-8.587523400000002</v>
       </c>
       <c r="Q77">
-        <v>-8.418567500000002</v>
+        <v>-8.562523400000002</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2448317128695361</v>
+        <v>0.2531247009057667</v>
       </c>
       <c r="T77">
-        <v>1.924788779882638</v>
+        <v>2.004988312377748</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05448717280778348</v>
+        <v>0.05377023632347055</v>
       </c>
       <c r="W77">
-        <v>0.2229519246519247</v>
+        <v>0.2231209782749257</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2179486912311339</v>
+        <v>0.2150809452938821</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2303218717063275</v>
+        <v>0.2322218717063275</v>
       </c>
       <c r="C78">
-        <v>-34.19518467576183</v>
+        <v>-35.25540980318873</v>
       </c>
       <c r="D78">
-        <v>24.15881532423818</v>
+        <v>23.91259019681127</v>
       </c>
       <c r="E78">
-        <v>34.864</v>
+        <v>35.678</v>
       </c>
       <c r="F78">
-        <v>61.864</v>
+        <v>62.678</v>
       </c>
       <c r="G78">
         <v>3.51</v>
@@ -7683,37 +7683,37 @@
         <v>3.1375</v>
       </c>
       <c r="M78">
-        <v>14.5875312</v>
+        <v>14.7794724</v>
       </c>
       <c r="N78">
-        <v>-11.4500312</v>
+        <v>-11.6419724</v>
       </c>
       <c r="O78">
-        <v>-2.8625078</v>
+        <v>-2.9104931</v>
       </c>
       <c r="P78">
-        <v>-8.587523400000002</v>
+        <v>-8.731479300000002</v>
       </c>
       <c r="Q78">
-        <v>-8.562523400000002</v>
+        <v>-8.706479300000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2531247009057667</v>
+        <v>0.2621388183364523</v>
       </c>
       <c r="T78">
-        <v>2.004988312377748</v>
+        <v>2.092161717263738</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05377023632347055</v>
+        <v>0.05307192156602288</v>
       </c>
       <c r="W78">
-        <v>0.2231209782749257</v>
+        <v>0.2232856408947318</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2150809452938821</v>
+        <v>0.2122876862640914</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2322218717063275</v>
+        <v>0.2341218717063275</v>
       </c>
       <c r="C79">
-        <v>-35.25540980318873</v>
+        <v>-36.31066654603159</v>
       </c>
       <c r="D79">
-        <v>23.91259019681127</v>
+        <v>23.67133345396842</v>
       </c>
       <c r="E79">
-        <v>35.678</v>
+        <v>36.492</v>
       </c>
       <c r="F79">
-        <v>62.678</v>
+        <v>63.492</v>
       </c>
       <c r="G79">
         <v>3.51</v>
@@ -7765,37 +7765,37 @@
         <v>3.1375</v>
       </c>
       <c r="M79">
-        <v>14.7794724</v>
+        <v>14.9714136</v>
       </c>
       <c r="N79">
-        <v>-11.6419724</v>
+        <v>-11.8339136</v>
       </c>
       <c r="O79">
-        <v>-2.9104931</v>
+        <v>-2.958478400000001</v>
       </c>
       <c r="P79">
-        <v>-8.731479300000002</v>
+        <v>-8.875435200000002</v>
       </c>
       <c r="Q79">
-        <v>-8.706479300000002</v>
+        <v>-8.850435200000002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2621388183364523</v>
+        <v>0.2719724009881092</v>
       </c>
       <c r="T79">
-        <v>2.092161717263738</v>
+        <v>2.187259977139362</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05307192156602288</v>
+        <v>0.05239151231517643</v>
       </c>
       <c r="W79">
-        <v>0.2232856408947318</v>
+        <v>0.2234460813960814</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2122876862640914</v>
+        <v>0.2095660492607057</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2341218717063275</v>
+        <v>0.2360218717063275</v>
       </c>
       <c r="C80">
-        <v>-36.31066654603159</v>
+        <v>-37.36110378197666</v>
       </c>
       <c r="D80">
-        <v>23.67133345396842</v>
+        <v>23.43489621802335</v>
       </c>
       <c r="E80">
-        <v>36.492</v>
+        <v>37.30600000000001</v>
       </c>
       <c r="F80">
-        <v>63.492</v>
+        <v>64.30600000000001</v>
       </c>
       <c r="G80">
         <v>3.51</v>
@@ -7847,37 +7847,37 @@
         <v>3.1375</v>
       </c>
       <c r="M80">
-        <v>14.9714136</v>
+        <v>15.1633548</v>
       </c>
       <c r="N80">
-        <v>-11.8339136</v>
+        <v>-12.0258548</v>
       </c>
       <c r="O80">
-        <v>-2.958478400000001</v>
+        <v>-3.006463700000001</v>
       </c>
       <c r="P80">
-        <v>-8.875435200000002</v>
+        <v>-9.019391100000004</v>
       </c>
       <c r="Q80">
-        <v>-8.850435200000002</v>
+        <v>-8.994391100000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2719724009881092</v>
+        <v>0.2827425153208763</v>
       </c>
       <c r="T80">
-        <v>2.187259977139362</v>
+        <v>2.291415214145998</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05239151231517643</v>
+        <v>0.05172832861498431</v>
       </c>
       <c r="W80">
-        <v>0.2234460813960814</v>
+        <v>0.2236024601125867</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2095660492607057</v>
+        <v>0.2069133144599372</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2360218717063275</v>
+        <v>0.2379218717063275</v>
       </c>
       <c r="C81">
-        <v>-37.36110378197666</v>
+        <v>-38.4068644993733</v>
       </c>
       <c r="D81">
-        <v>23.43489621802335</v>
+        <v>23.20313550062671</v>
       </c>
       <c r="E81">
-        <v>37.30600000000001</v>
+        <v>38.12</v>
       </c>
       <c r="F81">
-        <v>64.30600000000001</v>
+        <v>65.12</v>
       </c>
       <c r="G81">
         <v>3.51</v>
@@ -7929,37 +7929,37 @@
         <v>3.1375</v>
       </c>
       <c r="M81">
-        <v>15.1633548</v>
+        <v>15.355296</v>
       </c>
       <c r="N81">
-        <v>-12.0258548</v>
+        <v>-12.217796</v>
       </c>
       <c r="O81">
-        <v>-3.006463700000001</v>
+        <v>-3.054449</v>
       </c>
       <c r="P81">
-        <v>-9.019391100000004</v>
+        <v>-9.163347000000002</v>
       </c>
       <c r="Q81">
-        <v>-8.994391100000003</v>
+        <v>-9.138347000000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2827425153208763</v>
+        <v>0.2945896410869201</v>
       </c>
       <c r="T81">
-        <v>2.291415214145998</v>
+        <v>2.405985974853298</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05172832861498431</v>
+        <v>0.05108172450729702</v>
       </c>
       <c r="W81">
-        <v>0.2236024601125867</v>
+        <v>0.2237549293611794</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2069133144599372</v>
+        <v>0.204326898029188</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2379218717063275</v>
+        <v>0.2398218717063275</v>
       </c>
       <c r="C82">
-        <v>-38.4068644993733</v>
+        <v>-39.44808608559694</v>
       </c>
       <c r="D82">
-        <v>23.20313550062671</v>
+        <v>22.97591391440307</v>
       </c>
       <c r="E82">
-        <v>38.12</v>
+        <v>38.93400000000001</v>
       </c>
       <c r="F82">
-        <v>65.12</v>
+        <v>65.93400000000001</v>
       </c>
       <c r="G82">
         <v>3.51</v>
@@ -8011,37 +8011,37 @@
         <v>3.1375</v>
       </c>
       <c r="M82">
-        <v>15.355296</v>
+        <v>15.5472372</v>
       </c>
       <c r="N82">
-        <v>-12.217796</v>
+        <v>-12.4097372</v>
       </c>
       <c r="O82">
-        <v>-3.054449</v>
+        <v>-3.102434300000001</v>
       </c>
       <c r="P82">
-        <v>-9.163347000000002</v>
+        <v>-9.307302900000003</v>
       </c>
       <c r="Q82">
-        <v>-9.138347000000001</v>
+        <v>-9.282302900000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2945896410869201</v>
+        <v>0.3076838327230738</v>
       </c>
       <c r="T82">
-        <v>2.405985974853298</v>
+        <v>2.532616815635051</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05108172450729702</v>
+        <v>0.05045108593313285</v>
       </c>
       <c r="W82">
-        <v>0.2237549293611794</v>
+        <v>0.2239036339369673</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.204326898029188</v>
+        <v>0.2018043437325314</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2398218717063275</v>
+        <v>0.2417218717063275</v>
       </c>
       <c r="C83">
-        <v>-39.44808608559694</v>
+        <v>-40.48490059863303</v>
       </c>
       <c r="D83">
-        <v>22.97591391440307</v>
+        <v>22.75309940136698</v>
       </c>
       <c r="E83">
-        <v>38.93400000000001</v>
+        <v>39.748</v>
       </c>
       <c r="F83">
-        <v>65.93400000000001</v>
+        <v>66.748</v>
       </c>
       <c r="G83">
         <v>3.51</v>
@@ -8093,37 +8093,37 @@
         <v>3.1375</v>
       </c>
       <c r="M83">
-        <v>15.5472372</v>
+        <v>15.7391784</v>
       </c>
       <c r="N83">
-        <v>-12.4097372</v>
+        <v>-12.6016784</v>
       </c>
       <c r="O83">
-        <v>-3.102434300000001</v>
+        <v>-3.150419600000001</v>
       </c>
       <c r="P83">
-        <v>-9.307302900000003</v>
+        <v>-9.451258800000002</v>
       </c>
       <c r="Q83">
-        <v>-9.282302900000003</v>
+        <v>-9.426258800000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3076838327230738</v>
+        <v>0.3222329345410224</v>
       </c>
       <c r="T83">
-        <v>2.532616815635051</v>
+        <v>2.673317749836998</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05045108593313285</v>
+        <v>0.04983582878760685</v>
       </c>
       <c r="W83">
-        <v>0.2239036339369673</v>
+        <v>0.2240487115718823</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2018043437325314</v>
+        <v>0.1993433151504274</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2417218717063275</v>
+        <v>0.2436218717063275</v>
       </c>
       <c r="C84">
-        <v>-40.48490059863303</v>
+        <v>-41.51743502301041</v>
       </c>
       <c r="D84">
-        <v>22.75309940136698</v>
+        <v>22.5345649769896</v>
       </c>
       <c r="E84">
-        <v>39.748</v>
+        <v>40.56200000000001</v>
       </c>
       <c r="F84">
-        <v>66.748</v>
+        <v>67.56200000000001</v>
       </c>
       <c r="G84">
         <v>3.51</v>
@@ -8175,37 +8175,37 @@
         <v>3.1375</v>
       </c>
       <c r="M84">
-        <v>15.7391784</v>
+        <v>15.9311196</v>
       </c>
       <c r="N84">
-        <v>-12.6016784</v>
+        <v>-12.7936196</v>
       </c>
       <c r="O84">
-        <v>-3.150419600000001</v>
+        <v>-3.198404900000001</v>
       </c>
       <c r="P84">
-        <v>-9.451258800000002</v>
+        <v>-9.595214700000003</v>
       </c>
       <c r="Q84">
-        <v>-9.426258800000001</v>
+        <v>-9.570214700000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3222329345410224</v>
+        <v>0.3384936953963766</v>
       </c>
       <c r="T84">
-        <v>2.673317749836998</v>
+        <v>2.830571735121528</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04983582878760685</v>
+        <v>0.049235397115467</v>
       </c>
       <c r="W84">
-        <v>0.2240487115718823</v>
+        <v>0.2241902933601729</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1993433151504274</v>
+        <v>0.1969415884618679</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2436218717063275</v>
+        <v>0.2455218717063275</v>
       </c>
       <c r="C85">
-        <v>-41.51743502301041</v>
+        <v>-42.54581151112602</v>
       </c>
       <c r="D85">
-        <v>22.5345649769896</v>
+        <v>22.32018848887398</v>
       </c>
       <c r="E85">
-        <v>40.56200000000001</v>
+        <v>41.376</v>
       </c>
       <c r="F85">
-        <v>67.56200000000001</v>
+        <v>68.376</v>
       </c>
       <c r="G85">
         <v>3.51</v>
@@ -8257,37 +8257,37 @@
         <v>3.1375</v>
       </c>
       <c r="M85">
-        <v>15.9311196</v>
+        <v>16.1230608</v>
       </c>
       <c r="N85">
-        <v>-12.7936196</v>
+        <v>-12.9855608</v>
       </c>
       <c r="O85">
-        <v>-3.198404900000001</v>
+        <v>-3.2463902</v>
       </c>
       <c r="P85">
-        <v>-9.595214700000003</v>
+        <v>-9.739170600000001</v>
       </c>
       <c r="Q85">
-        <v>-9.570214700000003</v>
+        <v>-9.714170600000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3384936953963766</v>
+        <v>0.3567870513586502</v>
       </c>
       <c r="T85">
-        <v>2.830571735121528</v>
+        <v>3.007482468566624</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.049235397115467</v>
+        <v>0.04864926143552097</v>
       </c>
       <c r="W85">
-        <v>0.2241902933601729</v>
+        <v>0.2243285041535042</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1969415884618679</v>
+        <v>0.1945970457420838</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2455218717063275</v>
+        <v>0.2474218717063275</v>
       </c>
       <c r="C86">
-        <v>-42.54581151112603</v>
+        <v>-43.57014761092491</v>
       </c>
       <c r="D86">
-        <v>22.32018848887398</v>
+        <v>22.10985238907508</v>
       </c>
       <c r="E86">
-        <v>41.376</v>
+        <v>42.19</v>
       </c>
       <c r="F86">
-        <v>68.376</v>
+        <v>69.19</v>
       </c>
       <c r="G86">
         <v>3.51</v>
@@ -8339,37 +8339,37 @@
         <v>3.1375</v>
       </c>
       <c r="M86">
-        <v>16.1230608</v>
+        <v>16.315002</v>
       </c>
       <c r="N86">
-        <v>-12.9855608</v>
+        <v>-13.177502</v>
       </c>
       <c r="O86">
-        <v>-3.2463902</v>
+        <v>-3.2943755</v>
       </c>
       <c r="P86">
-        <v>-9.739170600000001</v>
+        <v>-9.883126499999999</v>
       </c>
       <c r="Q86">
-        <v>-9.714170600000001</v>
+        <v>-9.858126499999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.35678705135865</v>
+        <v>0.3775195214492267</v>
       </c>
       <c r="T86">
-        <v>3.007482468566622</v>
+        <v>3.207981299804397</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04864926143552097</v>
+        <v>0.04807691718333838</v>
       </c>
       <c r="W86">
-        <v>0.2243285041535042</v>
+        <v>0.2244634629281688</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1945970457420838</v>
+        <v>0.1923076687333535</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2474218717063275</v>
+        <v>0.2493218717063275</v>
       </c>
       <c r="C87">
-        <v>-43.57014761092491</v>
+        <v>-44.5905564808269</v>
       </c>
       <c r="D87">
-        <v>22.10985238907508</v>
+        <v>21.9034435191731</v>
       </c>
       <c r="E87">
-        <v>42.19</v>
+        <v>43.004</v>
       </c>
       <c r="F87">
-        <v>69.19</v>
+        <v>70.004</v>
       </c>
       <c r="G87">
         <v>3.51</v>
@@ -8421,37 +8421,37 @@
         <v>3.1375</v>
       </c>
       <c r="M87">
-        <v>16.315002</v>
+        <v>16.5069432</v>
       </c>
       <c r="N87">
-        <v>-13.177502</v>
+        <v>-13.3694432</v>
       </c>
       <c r="O87">
-        <v>-3.2943755</v>
+        <v>-3.342360800000001</v>
       </c>
       <c r="P87">
-        <v>-9.883126499999999</v>
+        <v>-10.0270824</v>
       </c>
       <c r="Q87">
-        <v>-9.858126499999999</v>
+        <v>-10.0020824</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3775195214492267</v>
+        <v>0.4012137729813143</v>
       </c>
       <c r="T87">
-        <v>3.207981299804397</v>
+        <v>3.437122821218997</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04807691718333838</v>
+        <v>0.04751788326260187</v>
       </c>
       <c r="W87">
-        <v>0.2244634629281688</v>
+        <v>0.2245952831266785</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1923076687333535</v>
+        <v>0.1900715330504075</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2493218717063275</v>
+        <v>0.2512218717063275</v>
       </c>
       <c r="C88">
-        <v>-44.5905564808269</v>
+        <v>-45.60714709272595</v>
       </c>
       <c r="D88">
-        <v>21.9034435191731</v>
+        <v>21.70085290727405</v>
       </c>
       <c r="E88">
-        <v>43.004</v>
+        <v>43.818</v>
       </c>
       <c r="F88">
-        <v>70.004</v>
+        <v>70.818</v>
       </c>
       <c r="G88">
         <v>3.51</v>
@@ -8503,37 +8503,37 @@
         <v>3.1375</v>
       </c>
       <c r="M88">
-        <v>16.5069432</v>
+        <v>16.6988844</v>
       </c>
       <c r="N88">
-        <v>-13.3694432</v>
+        <v>-13.5613844</v>
       </c>
       <c r="O88">
-        <v>-3.342360800000001</v>
+        <v>-3.3903461</v>
       </c>
       <c r="P88">
-        <v>-10.0270824</v>
+        <v>-10.1710383</v>
       </c>
       <c r="Q88">
-        <v>-10.0020824</v>
+        <v>-10.1460383</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4012137729813143</v>
+        <v>0.4285532939798769</v>
       </c>
       <c r="T88">
-        <v>3.437122821218997</v>
+        <v>3.701516884389688</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04751788326260187</v>
+        <v>0.04697170069636507</v>
       </c>
       <c r="W88">
-        <v>0.2245952831266785</v>
+        <v>0.2247240729757971</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1900715330504075</v>
+        <v>0.1878868027854603</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2512218717063275</v>
+        <v>0.2531218717063275</v>
       </c>
       <c r="C89">
-        <v>-45.60714709272595</v>
+        <v>-46.62002442382695</v>
       </c>
       <c r="D89">
-        <v>21.70085290727405</v>
+        <v>21.50197557617305</v>
       </c>
       <c r="E89">
-        <v>43.818</v>
+        <v>44.63200000000001</v>
       </c>
       <c r="F89">
-        <v>70.818</v>
+        <v>71.63200000000001</v>
       </c>
       <c r="G89">
         <v>3.51</v>
@@ -8585,37 +8585,37 @@
         <v>3.1375</v>
       </c>
       <c r="M89">
-        <v>16.6988844</v>
+        <v>16.8908256</v>
       </c>
       <c r="N89">
-        <v>-13.5613844</v>
+        <v>-13.7533256</v>
       </c>
       <c r="O89">
-        <v>-3.3903461</v>
+        <v>-3.438331400000001</v>
       </c>
       <c r="P89">
-        <v>-10.1710383</v>
+        <v>-10.3149942</v>
       </c>
       <c r="Q89">
-        <v>-10.1460383</v>
+        <v>-10.2899942</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4285532939798769</v>
+        <v>0.4604494018115335</v>
       </c>
       <c r="T89">
-        <v>3.701516884389688</v>
+        <v>4.009976624755497</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04697170069636507</v>
+        <v>0.04643793137027001</v>
       </c>
       <c r="W89">
-        <v>0.2247240729757971</v>
+        <v>0.2248499357828903</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1878868027854603</v>
+        <v>0.18575172548108</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2531218717063275</v>
+        <v>0.2550218717063275</v>
       </c>
       <c r="C90">
-        <v>-46.62002442382695</v>
+        <v>-47.62928963803016</v>
       </c>
       <c r="D90">
-        <v>21.50197557617305</v>
+        <v>21.30671036196986</v>
       </c>
       <c r="E90">
-        <v>44.63200000000001</v>
+        <v>45.44600000000001</v>
       </c>
       <c r="F90">
-        <v>71.63200000000001</v>
+        <v>72.44600000000001</v>
       </c>
       <c r="G90">
         <v>3.51</v>
@@ -8667,37 +8667,37 @@
         <v>3.1375</v>
       </c>
       <c r="M90">
-        <v>16.8908256</v>
+        <v>17.08276680000001</v>
       </c>
       <c r="N90">
-        <v>-13.7533256</v>
+        <v>-13.94526680000001</v>
       </c>
       <c r="O90">
-        <v>-3.438331400000001</v>
+        <v>-3.486316700000001</v>
       </c>
       <c r="P90">
-        <v>-10.3149942</v>
+        <v>-10.4589501</v>
       </c>
       <c r="Q90">
-        <v>-10.2899942</v>
+        <v>-10.4339501</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4604494018115335</v>
+        <v>0.4981448019762183</v>
       </c>
       <c r="T90">
-        <v>4.009976624755497</v>
+        <v>4.374519954278724</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04643793137027001</v>
+        <v>0.04591615686049169</v>
       </c>
       <c r="W90">
-        <v>0.2248499357828903</v>
+        <v>0.2249729702122961</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.18575172548108</v>
+        <v>0.1836646274419668</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2550218717063275</v>
+        <v>0.2569218717063275</v>
       </c>
       <c r="C91">
-        <v>-47.62928963803016</v>
+        <v>-48.63504025752094</v>
       </c>
       <c r="D91">
-        <v>21.30671036196986</v>
+        <v>21.11495974247907</v>
       </c>
       <c r="E91">
-        <v>45.44600000000001</v>
+        <v>46.26000000000001</v>
       </c>
       <c r="F91">
-        <v>72.44600000000001</v>
+        <v>73.26000000000001</v>
       </c>
       <c r="G91">
         <v>3.51</v>
@@ -8749,37 +8749,37 @@
         <v>3.1375</v>
       </c>
       <c r="M91">
-        <v>17.08276680000001</v>
+        <v>17.274708</v>
       </c>
       <c r="N91">
-        <v>-13.94526680000001</v>
+        <v>-14.137208</v>
       </c>
       <c r="O91">
-        <v>-3.486316700000001</v>
+        <v>-3.534302</v>
       </c>
       <c r="P91">
-        <v>-10.4589501</v>
+        <v>-10.602906</v>
       </c>
       <c r="Q91">
-        <v>-10.4339501</v>
+        <v>-10.577906</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4981448019762183</v>
+        <v>0.5433792821738401</v>
       </c>
       <c r="T91">
-        <v>4.374519954278724</v>
+        <v>4.811971949706597</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04591615686049169</v>
+        <v>0.04540597733981958</v>
       </c>
       <c r="W91">
-        <v>0.2249729702122961</v>
+        <v>0.2250932705432706</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1836646274419668</v>
+        <v>0.1816239093592783</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2569218717063275</v>
+        <v>0.2588218717063275</v>
       </c>
       <c r="C92">
-        <v>-48.63504025752094</v>
+        <v>-49.63737032517718</v>
       </c>
       <c r="D92">
-        <v>21.11495974247907</v>
+        <v>20.92662967482283</v>
       </c>
       <c r="E92">
-        <v>46.26000000000001</v>
+        <v>47.07400000000001</v>
       </c>
       <c r="F92">
-        <v>73.26000000000001</v>
+        <v>74.07400000000001</v>
       </c>
       <c r="G92">
         <v>3.51</v>
@@ -8831,37 +8831,37 @@
         <v>3.1375</v>
       </c>
       <c r="M92">
-        <v>17.274708</v>
+        <v>17.4666492</v>
       </c>
       <c r="N92">
-        <v>-14.137208</v>
+        <v>-14.3291492</v>
       </c>
       <c r="O92">
-        <v>-3.534302</v>
+        <v>-3.582287300000001</v>
       </c>
       <c r="P92">
-        <v>-10.602906</v>
+        <v>-10.7468619</v>
       </c>
       <c r="Q92">
-        <v>-10.577906</v>
+        <v>-10.7218619</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5433792821738401</v>
+        <v>0.5986658690820447</v>
       </c>
       <c r="T92">
-        <v>4.811971949706597</v>
+        <v>5.346635499673996</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04540597733981958</v>
+        <v>0.0449070105558655</v>
       </c>
       <c r="W92">
-        <v>0.2250932705432706</v>
+        <v>0.2252109269109269</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1816239093592783</v>
+        <v>0.179628042223462</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2588218717063275</v>
+        <v>0.2607218717063275</v>
       </c>
       <c r="C93">
-        <v>-49.63737032517718</v>
+        <v>-50.63637055836187</v>
       </c>
       <c r="D93">
-        <v>20.92662967482283</v>
+        <v>20.74162944163814</v>
       </c>
       <c r="E93">
-        <v>47.07400000000001</v>
+        <v>47.88800000000001</v>
       </c>
       <c r="F93">
-        <v>74.07400000000001</v>
+        <v>74.88800000000001</v>
       </c>
       <c r="G93">
         <v>3.51</v>
@@ -8913,37 +8913,37 @@
         <v>3.1375</v>
       </c>
       <c r="M93">
-        <v>17.4666492</v>
+        <v>17.6585904</v>
       </c>
       <c r="N93">
-        <v>-14.3291492</v>
+        <v>-14.5210904</v>
       </c>
       <c r="O93">
-        <v>-3.582287300000001</v>
+        <v>-3.630272600000001</v>
       </c>
       <c r="P93">
-        <v>-10.7468619</v>
+        <v>-10.8908178</v>
       </c>
       <c r="Q93">
-        <v>-10.7218619</v>
+        <v>-10.8658178</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5986658690820447</v>
+        <v>0.6677741027173003</v>
       </c>
       <c r="T93">
-        <v>5.346635499673996</v>
+        <v>6.014964937133247</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0449070105558655</v>
+        <v>0.04441889087591045</v>
       </c>
       <c r="W93">
-        <v>0.2252109269109269</v>
+        <v>0.2253260255314603</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.179628042223462</v>
+        <v>0.1776755635036418</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2607218717063275</v>
+        <v>0.2626218717063276</v>
       </c>
       <c r="C94">
-        <v>-50.63637055836187</v>
+        <v>-51.63212849462991</v>
       </c>
       <c r="D94">
-        <v>20.74162944163814</v>
+        <v>20.5598715053701</v>
       </c>
       <c r="E94">
-        <v>47.88800000000001</v>
+        <v>48.70200000000001</v>
       </c>
       <c r="F94">
-        <v>74.88800000000001</v>
+        <v>75.70200000000001</v>
       </c>
       <c r="G94">
         <v>3.51</v>
@@ -8995,37 +8995,37 @@
         <v>3.1375</v>
       </c>
       <c r="M94">
-        <v>17.6585904</v>
+        <v>17.8505316</v>
       </c>
       <c r="N94">
-        <v>-14.5210904</v>
+        <v>-14.7130316</v>
       </c>
       <c r="O94">
-        <v>-3.630272600000001</v>
+        <v>-3.678257900000001</v>
       </c>
       <c r="P94">
-        <v>-10.8908178</v>
+        <v>-11.0347737</v>
       </c>
       <c r="Q94">
-        <v>-10.8658178</v>
+        <v>-11.0097737</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6677741027173003</v>
+        <v>0.7566275459626292</v>
       </c>
       <c r="T94">
-        <v>6.014964937133247</v>
+        <v>6.874245642437999</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04441889087591045</v>
+        <v>0.04394126839337378</v>
       </c>
       <c r="W94">
-        <v>0.2253260255314603</v>
+        <v>0.2254386489128425</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1776755635036418</v>
+        <v>0.175765073573495</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2626218717063276</v>
+        <v>0.2645218717063275</v>
       </c>
       <c r="C95">
-        <v>-51.63212849462991</v>
+        <v>-52.62472862984021</v>
       </c>
       <c r="D95">
-        <v>20.5598715053701</v>
+        <v>20.38127137015979</v>
       </c>
       <c r="E95">
-        <v>48.70200000000001</v>
+        <v>49.51600000000001</v>
       </c>
       <c r="F95">
-        <v>75.70200000000001</v>
+        <v>76.51600000000001</v>
       </c>
       <c r="G95">
         <v>3.51</v>
@@ -9077,37 +9077,37 @@
         <v>3.1375</v>
       </c>
       <c r="M95">
-        <v>17.8505316</v>
+        <v>18.0424728</v>
       </c>
       <c r="N95">
-        <v>-14.7130316</v>
+        <v>-14.9049728</v>
       </c>
       <c r="O95">
-        <v>-3.678257900000001</v>
+        <v>-3.726243200000001</v>
       </c>
       <c r="P95">
-        <v>-11.0347737</v>
+        <v>-11.1787296</v>
       </c>
       <c r="Q95">
-        <v>-11.0097737</v>
+        <v>-11.1537296</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7566275459626292</v>
+        <v>0.8750988036230675</v>
       </c>
       <c r="T95">
-        <v>6.874245642437999</v>
+        <v>8.019953249511</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04394126839337378</v>
+        <v>0.04347380809131661</v>
       </c>
       <c r="W95">
-        <v>0.2254386489128425</v>
+        <v>0.2255488760520676</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.175765073573495</v>
+        <v>0.1738952323652664</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2645218717063275</v>
+        <v>0.2664218717063275</v>
       </c>
       <c r="C96">
-        <v>-52.62472862984021</v>
+        <v>-53.61425254913164</v>
       </c>
       <c r="D96">
-        <v>20.38127137015979</v>
+        <v>20.20574745086837</v>
       </c>
       <c r="E96">
-        <v>49.51600000000001</v>
+        <v>50.33000000000001</v>
       </c>
       <c r="F96">
-        <v>76.51600000000001</v>
+        <v>77.33000000000001</v>
       </c>
       <c r="G96">
         <v>3.51</v>
@@ -9159,37 +9159,37 @@
         <v>3.1375</v>
       </c>
       <c r="M96">
-        <v>18.0424728</v>
+        <v>18.234414</v>
       </c>
       <c r="N96">
-        <v>-14.9049728</v>
+        <v>-15.09691400000001</v>
       </c>
       <c r="O96">
-        <v>-3.726243200000001</v>
+        <v>-3.774228500000001</v>
       </c>
       <c r="P96">
-        <v>-11.1787296</v>
+        <v>-11.3226855</v>
       </c>
       <c r="Q96">
-        <v>-11.1537296</v>
+        <v>-11.2976855</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8750988036230675</v>
+        <v>1.040958564347682</v>
       </c>
       <c r="T96">
-        <v>8.019953249511</v>
+        <v>9.623943899413204</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04347380809131661</v>
+        <v>0.04301618905877643</v>
       </c>
       <c r="W96">
-        <v>0.2255488760520676</v>
+        <v>0.2256567826199405</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1738952323652664</v>
+        <v>0.1720647562351056</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2664218717063275</v>
+        <v>0.2683218717063275</v>
       </c>
       <c r="C97">
-        <v>-53.61425254913164</v>
+        <v>-54.60077905118855</v>
       </c>
       <c r="D97">
-        <v>20.20574745086837</v>
+        <v>20.03322094881146</v>
       </c>
       <c r="E97">
-        <v>50.33000000000001</v>
+        <v>51.14400000000001</v>
       </c>
       <c r="F97">
-        <v>77.33000000000001</v>
+        <v>78.14400000000001</v>
       </c>
       <c r="G97">
         <v>3.51</v>
@@ -9241,37 +9241,37 @@
         <v>3.1375</v>
       </c>
       <c r="M97">
-        <v>18.234414</v>
+        <v>18.4263552</v>
       </c>
       <c r="N97">
-        <v>-15.09691400000001</v>
+        <v>-15.2888552</v>
       </c>
       <c r="O97">
-        <v>-3.774228500000001</v>
+        <v>-3.822213800000001</v>
       </c>
       <c r="P97">
-        <v>-11.3226855</v>
+        <v>-11.4666414</v>
       </c>
       <c r="Q97">
-        <v>-11.2976855</v>
+        <v>-11.4416414</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.040958564347682</v>
+        <v>1.289748205434603</v>
       </c>
       <c r="T97">
-        <v>9.623943899413204</v>
+        <v>12.02992987426651</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04301618905877643</v>
+        <v>0.04256810375608085</v>
       </c>
       <c r="W97">
-        <v>0.2256567826199405</v>
+        <v>0.2257624411343161</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1720647562351056</v>
+        <v>0.1702724150243233</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2683218717063275</v>
+        <v>0.2702218717063275</v>
       </c>
       <c r="C98">
-        <v>-54.60077905118855</v>
+        <v>-55.58438426619428</v>
       </c>
       <c r="D98">
-        <v>20.03322094881146</v>
+        <v>19.86361573380572</v>
       </c>
       <c r="E98">
-        <v>51.14400000000001</v>
+        <v>51.958</v>
       </c>
       <c r="F98">
-        <v>78.14400000000001</v>
+        <v>78.958</v>
       </c>
       <c r="G98">
         <v>3.51</v>
@@ -9323,37 +9323,37 @@
         <v>3.1375</v>
       </c>
       <c r="M98">
-        <v>18.4263552</v>
+        <v>18.6182964</v>
       </c>
       <c r="N98">
-        <v>-15.2888552</v>
+        <v>-15.4807964</v>
       </c>
       <c r="O98">
-        <v>-3.822213800000001</v>
+        <v>-3.870199100000001</v>
       </c>
       <c r="P98">
-        <v>-11.4666414</v>
+        <v>-11.6105973</v>
       </c>
       <c r="Q98">
-        <v>-11.4416414</v>
+        <v>-11.5855973</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.289748205434599</v>
+        <v>1.704397607246132</v>
       </c>
       <c r="T98">
-        <v>12.02992987426648</v>
+        <v>16.03990649902197</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04256810375608085</v>
+        <v>0.04212925732560579</v>
       </c>
       <c r="W98">
-        <v>0.2257624411343161</v>
+        <v>0.2258659211226222</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1702724150243233</v>
+        <v>0.1685170293024231</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2702218717063275</v>
+        <v>0.2721218717063275</v>
       </c>
       <c r="C99">
-        <v>-55.58438426619428</v>
+        <v>-56.56514176784309</v>
       </c>
       <c r="D99">
-        <v>19.86361573380572</v>
+        <v>19.69685823215691</v>
       </c>
       <c r="E99">
-        <v>51.958</v>
+        <v>52.77200000000001</v>
       </c>
       <c r="F99">
-        <v>78.958</v>
+        <v>79.77200000000001</v>
       </c>
       <c r="G99">
         <v>3.51</v>
@@ -9405,37 +9405,37 @@
         <v>3.1375</v>
       </c>
       <c r="M99">
-        <v>18.6182964</v>
+        <v>18.8102376</v>
       </c>
       <c r="N99">
-        <v>-15.4807964</v>
+        <v>-15.6727376</v>
       </c>
       <c r="O99">
-        <v>-3.870199100000001</v>
+        <v>-3.9181844</v>
       </c>
       <c r="P99">
-        <v>-11.6105973</v>
+        <v>-11.7545532</v>
       </c>
       <c r="Q99">
-        <v>-11.5855973</v>
+        <v>-11.7295532</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.704397607246132</v>
+        <v>2.533696410869198</v>
       </c>
       <c r="T99">
-        <v>16.03990649902197</v>
+        <v>24.05985974853295</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04212925732560579</v>
+        <v>0.04169936694473226</v>
       </c>
       <c r="W99">
-        <v>0.2258659211226222</v>
+        <v>0.2259672892744321</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1685170293024231</v>
+        <v>0.166797467778929</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2721218717063275</v>
+        <v>0.2740218717063275</v>
       </c>
       <c r="C100">
-        <v>-56.56514176784309</v>
+        <v>-57.54312267975698</v>
       </c>
       <c r="D100">
-        <v>19.69685823215691</v>
+        <v>19.53287732024302</v>
       </c>
       <c r="E100">
-        <v>52.77200000000001</v>
+        <v>53.586</v>
       </c>
       <c r="F100">
-        <v>79.77200000000001</v>
+        <v>80.586</v>
       </c>
       <c r="G100">
         <v>3.51</v>
@@ -9487,37 +9487,37 @@
         <v>3.1375</v>
       </c>
       <c r="M100">
-        <v>18.8102376</v>
+        <v>19.0021788</v>
       </c>
       <c r="N100">
-        <v>-15.6727376</v>
+        <v>-15.8646788</v>
       </c>
       <c r="O100">
-        <v>-3.9181844</v>
+        <v>-3.9661697</v>
       </c>
       <c r="P100">
-        <v>-11.7545532</v>
+        <v>-11.8985091</v>
       </c>
       <c r="Q100">
-        <v>-11.7295532</v>
+        <v>-11.8735091</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.533696410869198</v>
+        <v>5.021592821738396</v>
       </c>
       <c r="T100">
-        <v>24.05985974853295</v>
+        <v>48.11971949706592</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04169936694473226</v>
+        <v>0.0412781612180178</v>
       </c>
       <c r="W100">
-        <v>0.2259672892744321</v>
+        <v>0.2260666095847914</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.166797467778929</v>
+        <v>0.1651126448720711</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2740218717063275</v>
-      </c>
-      <c r="C101">
-        <v>-57.54312267975698</v>
-      </c>
-      <c r="D101">
-        <v>19.53287732024302</v>
-      </c>
-      <c r="E101">
-        <v>53.586</v>
-      </c>
-      <c r="F101">
-        <v>80.586</v>
-      </c>
-      <c r="G101">
-        <v>3.51</v>
-      </c>
-      <c r="H101">
-        <v>54.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.1625</v>
-      </c>
-      <c r="K101">
-        <v>0.025</v>
-      </c>
-      <c r="L101">
-        <v>3.1375</v>
-      </c>
-      <c r="M101">
-        <v>19.0021788</v>
-      </c>
-      <c r="N101">
-        <v>-15.8646788</v>
-      </c>
-      <c r="O101">
-        <v>-3.9661697</v>
-      </c>
-      <c r="P101">
-        <v>-11.8985091</v>
-      </c>
-      <c r="Q101">
-        <v>-11.8735091</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.021592821738396</v>
-      </c>
-      <c r="T101">
-        <v>48.11971949706592</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0412781612180178</v>
-      </c>
-      <c r="W101">
-        <v>0.2260666095847914</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1651126448720711</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
